--- a/lib/davinci_crd_test_kit/requirements/hl7.fhir.us.davinci-crd_2.0.1_requirements.xlsx
+++ b/lib/davinci_crd_test_kit/requirements/hl7.fhir.us.davinci-crd_2.0.1_requirements.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11130"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/knaden/Documents/Inferno/source/davinci-crd-test-kit/lib/davinci_crd_test_kit/requirements/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/karlnaden/GlenViewAssociates/Inferno/source/davinci-crd-test-kit/lib/davinci_crd_test_kit/requirements/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AE216CD-C581-0E41-8635-FE85C4BEB01D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F22370C-3EBF-A84B-A177-C594769D23FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="300" yWindow="5620" windowWidth="34560" windowHeight="20180" activeTab="1" xr2:uid="{D251129A-65BB-5042-909C-749E11B8C0B0}"/>
+    <workbookView xWindow="160" yWindow="920" windowWidth="34240" windowHeight="21260" activeTab="1" xr2:uid="{D251129A-65BB-5042-909C-749E11B8C0B0}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="9" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="Column Data" sheetId="7" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Requirements!$A$1:$T$312</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Requirements!$A$1:$T$433</definedName>
     <definedName name="EXPLODE" localSheetId="0">_xlfn.LAMBDA(_xlpm.string,_xlfn.MAKEARRAY(1,LEN(_xlpm.string),_xlfn.LAMBDA(_xlpm.r,_xlpm.c,MID(_xlpm.string,_xlpm.c,1))))</definedName>
     <definedName name="EXPLODE">_xlfn.LAMBDA(_xlpm.string,_xlfn.MAKEARRAY(1,LEN(_xlpm.string),_xlfn.LAMBDA(_xlpm.r,_xlpm.c,MID(_xlpm.string,_xlpm.c,1))))</definedName>
     <definedName name="FIND_DUPLICATES" localSheetId="0">_xlfn.LAMBDA(_xlpm.test_word,_xlpm.test_key,_xlpm.words,_xlpm.keys,_xlpm.threshold, _xlfn.LET(_xlpm.duplist,_xlfn._xlws.FILTER(_xlpm.keys,_xlfn.BYROW(_xlpm.words, _xlfn.LAMBDA(_xlpm.word, Info!HAMDIST(INDEX(_xlpm.word,1,1), _xlpm.test_word)&lt;_xlpm.threshold))),_xlfn.SINGLE(_xlfn._xlws.FILTER(_xlpm.duplist,_xlpm.duplist&lt;&gt;_xlpm.test_key,""))))</definedName>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1410" uniqueCount="450">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1583" uniqueCount="505">
   <si>
     <r>
       <rPr>
@@ -1701,74 +1701,6 @@
     <t>[In response to an [appointment-book](https://cds-hooks.hl7.org/hooks/appointment-book/STU1/appointment-book/) hook call, Servers may return] Reminders about additional services that are recommended to be scheduled or booked for the same patient - either as part of the scheduled encounter or as part of additional appointments that could be created at the same time</t>
   </si>
   <si>
-    <t>[For the appointment-book hook] The profiles expected to be used for the resources resolved to by the userId … are … [profile-practitioner](https://hl7.org/fhir/us/davinci-crd/STU2/StructureDefinition-profile-practitioner.html) [or] [us-core-practitionerrole](http://hl7.org/fhir/us/core/STU3.1.1/StructureDefinition-us-core-practitionerrole.html)</t>
-  </si>
-  <si>
-    <t>[For the appointment-book hook] The profiles expected to be used for the resources resolved to by the … patientId … are … [profile-patient](https://hl7.org/fhir/us/davinci-crd/STU2/StructureDefinition-profile-patient.html)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">[For the appointment-book hook] The profiles expected to be used for the resources resolved to by the … encounterId … are … </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[profile-encounter]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(https://hl7.org/fhir/us/davinci-crd/STU2/StructureDefinition-profile-encounter.html)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>[for the appointment-book hook] The profiles expected to be used for the resources resolved to by the … `appointments` … are …</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[profile-appointment</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>](https://hl7.org/fhir/us/davinci-crd/STU2/StructureDefinition-profile-appointment.html)</t>
-    </r>
-  </si>
-  <si>
-    <t>While this [[appointment-book](https://cds-hooks.hl7.org/hooks/appointment-book/2023SepSTU1Ballot/appointment-book/)] hook supports userIds of Patient and RelatedPerson, for CRD purposes it is enough to support Practitioner and PractitionerRole. [For the appointment-book hooks] upport for Patient and RelatedPerson as users is optional [([published v1.0 link](https://cds-hooks.hl7.org/hooks/appointment-book/STU1/appointment-book/))]</t>
-  </si>
-  <si>
     <t xml:space="preserve">CRD Servers MAY use this [[appointment-book](https://cds-hooks.hl7.org/hooks/appointment-book/STU1/appointment-book/)]  hook as a basis for associating a patient with a particular practitioner from a payer attribution perspective. </t>
   </si>
   <si>
@@ -1802,15 +1734,6 @@
     <t>The advice returned [by servers] for this [[encounter-start](https://cds-hooks.hl7.org/hooks/encounter-start/STU1/encounter-start)] hook would include the same sorts of advice as provided for using appointment-book [including: "Reminders about additional services that are recommended to be scheduled or booked for the same patient - either as part of the scheduled encounter or as part of additional appointments that could be created at the same time"]</t>
   </si>
   <si>
-    <t>[For the enounter-start hook] The profiles expected to be used for the resources resolved to by the userId … are … [profile-practitioner](https://hl7.org/fhir/us/davinci-crd/STU2/StructureDefinition-profile-practitioner.html) [or] [us-core-practitionerrole](http://hl7.org/fhir/us/core/STU3.1.1/StructureDefinition-us-core-practitionerrole.html)</t>
-  </si>
-  <si>
-    <t>[For the enounter-start hook] The profiles expected to be used for the resources resolved to by the … patientId … are … [profile-patient](https://hl7.org/fhir/us/davinci-crd/STU2/StructureDefinition-profile-patient.html)</t>
-  </si>
-  <si>
-    <t>[For the enounter-start hook] The profiles expected to be used for the resources resolved to by the … encounterId … are … [profile-encounter](https://hl7.org/fhir/us/davinci-crd/STU2/StructureDefinition-profile-encounter.html)</t>
-  </si>
-  <si>
     <t>CRD Servers MAY use this [[encounter-start](https://cds-hooks.hl7.org/hooks/encounter-start/STU1/encounter-start)] hook as a basis for associating a patient with a particular practitioner from a payer attribution perspective.</t>
   </si>
   <si>
@@ -1826,21 +1749,6 @@
     <t>This  [[encounter-discharge](https://cds-hooks.hl7.org/hooks/encounter-discharge/STU1/encounter-discharge/)] hook would generally be specific to an in-patient encounter and would fire when a provider is performing the discharge process within the CRD Client.</t>
   </si>
   <si>
-    <t>[In response to an [encounter-discharge](https://cds-hooks.hl7.org/hooks/encounter-discharge/STU1/encounter-discharge/) hook call, [clients should] Verify that documentation requirements for the services performed have been met to ensure the services provided can be reimbursed</t>
-  </si>
-  <si>
-    <t>[In response to an [encounter-discharge](https://cds-hooks.hl7.org/hooks/encounter-discharge/STU1/encounter-discharge/) hook call, [clients should] Ensure that required follow-up planning is complete and appropriate transfer of care has been arranged, particularly for accountable care models</t>
-  </si>
-  <si>
-    <t>[for the [encounter-discharge](https://cds-hooks.hl7.org/hooks/encounter-discharge/STU1/encounter-discharge/) hook] The profiles expected to be used for the resources resolved to by the userId … are … [profile-practitioner](https://hl7.org/fhir/us/davinci-crd/STU2/StructureDefinition-profile-practitioner.html) [or] [us-core-practitionerrole](http://hl7.org/fhir/us/core/STU3.1.1/StructureDefinition-us-core-practitionerrole.html)</t>
-  </si>
-  <si>
-    <t>[for the [encounter-discharge](https://cds-hooks.hl7.org/hooks/encounter-discharge/STU1/encounter-discharge/) hook] The profiles expected to be used for the resources resolved to by the … patientId … are … [profile-patient](https://hl7.org/fhir/us/davinci-crd/STU2/StructureDefinition-profile-patient.html)</t>
-  </si>
-  <si>
-    <t>[for the [encounter-discharge](https://cds-hooks.hl7.org/hooks/encounter-discharge/STU1/encounter-discharge/) hook] The profiles expected to be used for the resources resolved to by the … encounterId … are … [profile-encounter](https://hl7.org/fhir/us/davinci-crd/STU2/StructureDefinition-profile-encounter.html)</t>
-  </si>
-  <si>
     <t>https://hl7.org/fhir/us/davinci-crd/STU2/hooks.html#order-dispatch</t>
   </si>
   <si>
@@ -1862,67 +1770,10 @@
     <t>https://hl7.org/fhir/us/davinci-crd/STU2/hooks.html#order-select</t>
   </si>
   <si>
-    <t xml:space="preserve">[Servers SHALL support] version 1.0 of the [[order-select](https://cds-hooks.hl7.org/hooks/order-select/2023SepSTU1Ballot/order-select/)] Hook  [([published v1.0 link](https://cds-hooks.hl7.org/hooks/order-select/STU1/order-select/))] </t>
-  </si>
-  <si>
     <t xml:space="preserve"> conditional on supporting the indicated hook.</t>
   </si>
   <si>
-    <t xml:space="preserve">[Clients SHALL support] version 1.0 of the [[order-select](https://cds-hooks.hl7.org/hooks/order-select/2023SepSTU1Ballot/order-select/)] Hook [([published v1.0 link](https://cds-hooks.hl7.org/hooks/order-select/STU1/order-select/))] </t>
-  </si>
-  <si>
-    <t>Coverage requirements [returned from the [order-select hook](https://cds-hooks.hl7.org/hooks/order-select/STU1/order-select/)] SHOULD be limited only to those resources that are included in the `selections` context</t>
-  </si>
-  <si>
-    <t>the content of other [resources that are not included in the `selections` context] resources  [[for the order-select hook](https://cds-hooks.hl7.org/hooks/order-select/STU1/order-select/)] SHOULD also be considered before making recommendations about what additional actions are necessary. (I.e. don’t recommend an action if there’s already a draft order to perform that action.)</t>
-  </si>
-  <si>
-    <t>[For the [order-select](https://cds-hooks.hl7.org/hooks/order-select/STU1/order-select/) hook] the profiles expected to be used for the resources resolved to by the `patientId` [are] [profile-patient](https://hl7.org/fhir/us/davinci-crd/STU2/StructureDefinition-profile-patient.html)</t>
-  </si>
-  <si>
-    <t>[For the [order-select](https://cds-hooks.hl7.org/hooks/order-select/STU1/order-select/) hook] the profiles expected to be used for the resources resolved to by the … `encounterId` [are] [profile-encounter](https://hl7.org/fhir/us/davinci-crd/STU2/StructureDefinition-profile-encounter.html)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[for the [order-select](https://cds-hooks.hl7.org/hooks/order-select/STU1/order-select/) hook] The profiles expected to be used for the resources resolved to by the ... `draftOrders` context element [are] [profile-devicerequest](https://hl7.org/fhir/us/davinci-crd/STU2/StructureDefinition-profile-devicerequest.html), [profile-medicationrequest](https://hl7.org/fhir/us/davinci-crd/STU2/StructureDefinition-profile-medicationrequest.html), [profile-nutritionorder](https://hl7.org/fhir/us/davinci-crd/STU2/StructureDefinition-profile-nutritionorder.html), [profile-visionprescription](https://hl7.org/fhir/us/davinci-crd/STU2/StructureDefinition-profile-visionprescription.html), [and] [profile-servicerequest](https://hl7.org/fhir/us/davinci-crd/STU2/StructureDefinition-profile-servicerequest.html) </t>
-  </si>
-  <si>
-    <t>While this [order-select](https://cds-hooks.hl7.org/hooks/order-select/STU1/order-select/)] hook does not explicitly list PractitionerRole [([us-core-practitionerrole](http://hl7.org/fhir/us/core/STU3.1.1/StructureDefinition-us-core-practitionerrole.html)) in addition to  [profile-practitioner](https://hl7.org/fhir/us/davinci-crd/STU2/StructureDefinition-profile-practitioner.html)] as an expected resource type for userId, it is not prohibited and is included to allow linking the user to a Practitioner in a specific role acting on behalf of a specific Organization.</t>
-  </si>
-  <si>
-    <t>This [[order-select](https://cds-hooks.hl7.org/hooks/order-select/STU1/order-select/)] hook MAY be used in scenarios that don’t involve creating a true order</t>
-  </si>
-  <si>
     <t>https://hl7.org/fhir/us/davinci-crd/STU2/hooks.html#order-sign</t>
-  </si>
-  <si>
-    <t>[Servers SHALL support] version 1.0 of the [[order-sign](https://cds-hooks.org/hooks/order-sign/2020May/order-sign)] Hook. [([published v1.0 link](https://cds-hooks.hl7.org/hooks/order-sign/STU1/order-sign/))]</t>
-  </si>
-  <si>
-    <t>[Clients SHALL support] version 1.0 of the [[order-sign](https://cds-hooks.org/hooks/order-sign/2020May/order-sign)] Hook [([published v1.0 link](https://cds-hooks.hl7.org/hooks/order-sign/STU1/order-sign/))]</t>
-  </si>
-  <si>
-    <t>[[For the order-sign hook](https://cds-hooks.hl7.org/hooks/order-sign/STU1/order-sign/)] It’s appropriate to provide warnings if there is insufficient information to determine coverage requirements.</t>
-  </si>
-  <si>
-    <t>Use and profiles for [order-select](https://hl7.org/fhir/us/davinci-crd/STU2/hooks.html#order-select) also apply to [order-sign](https://cds-hooks.hl7.org/hooks/order-sign/STU1/order-sign/) [including: the profiles expected to be used for the resources resolved to by the `patientId`are [profile-patient](https://hl7.org/fhir/us/davinci-crd/STU2/StructureDefinition-profile-patient.html)]</t>
-  </si>
-  <si>
-    <t>Use and profiles for [order-select](https://hl7.org/fhir/us/davinci-crd/STU2/hooks.html#order-select) also apply to [order-sign](https://cds-hooks.hl7.org/hooks/order-sign/STU1/order-sign/) [including: the profiles expected to be used for the resources resolved to by the … `encounterId` are [profile-encounter](https://hl7.org/fhir/us/davinci-crd/STU2/StructureDefinition-profile-encounter.html)]</t>
-  </si>
-  <si>
-    <t>Use and profiles for [order-select](https://hl7.org/fhir/us/davinci-crd/STU2/hooks.html#order-select) also apply to [order-sign](https://cds-hooks.hl7.org/hooks/order-sign/STU1/order-sign/) [including: The profiles expected to be used for the resources resolved to by the ... `draftOrders` context element [are] [profile-devicerequest](https://hl7.org/fhir/us/davinci-crd/STU2/StructureDefinition-profile-devicerequest.html), [profile-medicationrequest](https://hl7.org/fhir/us/davinci-crd/STU2/StructureDefinition-profile-medicationrequest.html), [profile-nutritionorder](https://hl7.org/fhir/us/davinci-crd/STU2/StructureDefinition-profile-nutritionorder.html), [profile-visionprescription](https://hl7.org/fhir/us/davinci-crd/STU2/StructureDefinition-profile-visionprescription.html),  [profile-servicerequest](https://hl7.org/fhir/us/davinci-crd/STU2/StructureDefinition-profile-servicerequest.html)]</t>
-  </si>
-  <si>
-    <t>Use and profiles for [order-select](https://hl7.org/fhir/us/davinci-crd/STU2/hooks.html#order-select) also apply to [order-sign](https://cds-hooks.hl7.org/hooks/order-sign/STU1/order-sign/) [including: while this hook does not explicitly list PractitionerRole [([us-core-practitionerrole](http://hl7.org/fhir/us/core/STU3.1.1/StructureDefinition-us-core-practitionerrole.html)) in addition to  [profile-practitioner](https://hl7.org/fhir/us/davinci-crd/STU2/StructureDefinition-profile-practitioner.html)] as an expected resource type for userId, it is not prohibited and is included to allow linking the user to a Practitioner in a specific role acting on behalf of a specific Organization.]</t>
-  </si>
-  <si>
-    <t>CRD Servers MAY use this [[order-sign hook](https://cds-hooks.hl7.org/hooks/order-sign/STU1/order-sign/)] hook as a basis for associating a patient with a particular practitioner from a payer attribution perspective.</t>
-  </si>
-  <si>
-    <t>CRD clients ... SHALL, at minimum, support returning … processing the Coverage Information system action for all invocations of this [[order-sign hook](https://cds-hooks.hl7.org/hooks/order-sign/STU1/order-sign/)] hook.</t>
-  </si>
-  <si>
-    <t>CRD... servers SHALL, at minimum, support... processing the Coverage Information system action for all invocations of this [[order-sign hook](https://cds-hooks.hl7.org/hooks/order-sign/STU1/order-sign/)] hook.</t>
   </si>
   <si>
     <t>https://hl7.org/fhir/us/davinci-crd/STU2/cards.html#cards-profiles</t>
@@ -2982,6 +2833,324 @@
   </si>
   <si>
     <t>this is text describing and the requirement is actually in requirement 135, so marked as DEPRECATED.</t>
+  </si>
+  <si>
+    <t>conditional on requirement 20: if clients allow users to continue their workflow before long-running CRD results return, then this is a requirement.</t>
+  </si>
+  <si>
+    <t>[Clients SHALL support] version 1.1 of the [[order-sign](https://cds-hooks.org/hooks/order-sign/2020May/order-sign)] Hook [([published v1.0 link (v1.1.0 in the change log)](https://cds-hooks.hl7.org/hooks/STU1/order-sign.html))]</t>
+  </si>
+  <si>
+    <t>[Servers SHALL support] version 1.1 of the [[order-sign](https://cds-hooks.org/hooks/order-sign/2020May/order-sign)] Hook [([published v1.0 link (v1.1.0 in the change log)](https://cds-hooks.hl7.org/hooks/STU1/order-sign.html))]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Servers SHALL support] version 1.0 of the [[order-select](https://cds-hooks.hl7.org/hooks/order-select/2023SepSTU1Ballot/order-select/)] Hook  [([published v1.0 link](https://cds-hooks.hl7.org/hooks/order-select.html))] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Clients SHALL support] version 1.0 of the [[order-select](https://cds-hooks.hl7.org/hooks/order-select/2023SepSTU1Ballot/order-select/)] Hook [([published v1.0 link](https://cds-hooks.hl7.org/hooks/order-select.html))] </t>
+  </si>
+  <si>
+    <t>Coverage requirements [returned from the [order-select hook](https://cds-hooks.hl7.org/hooks/order-select.html)] SHOULD be limited only to those resources that are included in the `selections` context</t>
+  </si>
+  <si>
+    <t>the content of other [resources that are not included in the `selections` context] resources  [[for the order-select hook](https://cds-hooks.hl7.org/hooks/order-select.html)] SHOULD also be considered before making recommendations about what additional actions are necessary. (I.e. don’t recommend an action if there’s already a draft order to perform that action.)</t>
+  </si>
+  <si>
+    <t>[For the [order-select](https://cds-hooks.hl7.org/hooks/order-select.html) hook] the profiles expected to be used for the resources resolved to by the `patientId` [are] [profile-patient](https://hl7.org/fhir/us/davinci-crd/STU2/StructureDefinition-profile-patient.html)</t>
+  </si>
+  <si>
+    <t>[For the [order-select](https://cds-hooks.hl7.org/hooks/order-select.html) hook] the profiles expected to be used for the resources resolved to by the … `encounterId` [are] [profile-encounter](https://hl7.org/fhir/us/davinci-crd/STU2/StructureDefinition-profile-encounter.html)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[for the [order-select](https://cds-hooks.hl7.org/hooks/order-select.html) hook] The profiles expected to be used for the resources resolved to by the ... `draftOrders` context element [are] [profile-devicerequest](https://hl7.org/fhir/us/davinci-crd/STU2/StructureDefinition-profile-devicerequest.html), [profile-medicationrequest](https://hl7.org/fhir/us/davinci-crd/STU2/StructureDefinition-profile-medicationrequest.html), [profile-nutritionorder](https://hl7.org/fhir/us/davinci-crd/STU2/StructureDefinition-profile-nutritionorder.html), [profile-visionprescription](https://hl7.org/fhir/us/davinci-crd/STU2/StructureDefinition-profile-visionprescription.html), [and] [profile-servicerequest](https://hl7.org/fhir/us/davinci-crd/STU2/StructureDefinition-profile-servicerequest.html) </t>
+  </si>
+  <si>
+    <t>While this [order-select](https://cds-hooks.hl7.org/hooks/order-select.html)] hook does not explicitly list PractitionerRole [([us-core-practitionerrole](http://hl7.org/fhir/us/core/STU3.1.1/StructureDefinition-us-core-practitionerrole.html)) in addition to  [profile-practitioner](https://hl7.org/fhir/us/davinci-crd/STU2/StructureDefinition-profile-practitioner.html)] as an expected resource type for userId, it is not prohibited and is included to allow linking the user to a Practitioner in a specific role acting on behalf of a specific Organization.</t>
+  </si>
+  <si>
+    <t>This [[order-select](https://cds-hooks.hl7.org/hooks/order-select.html)] hook MAY be used in scenarios that don’t involve creating a true order</t>
+  </si>
+  <si>
+    <t>[[For the order-sign hook](https://cds-hooks.hl7.org/hooks/STU1/order-sign.html)] It’s appropriate to provide warnings if there is insufficient information to determine coverage requirements.</t>
+  </si>
+  <si>
+    <t>CRD Servers MAY use this [[order-sign hook](https://cds-hooks.hl7.org/hooks/STU1/order-sign.html)] hook as a basis for associating a patient with a particular practitioner from a payer attribution perspective.</t>
+  </si>
+  <si>
+    <t>CRD clients ... SHALL, at minimum, support … processing the Coverage Information system action for all invocations of this [[order-sign hook](https://cds-hooks.hl7.org/hooks/STU1/order-sign.html)] hook.</t>
+  </si>
+  <si>
+    <t>CRD... servers SHALL, at minimum, support returning ... the Coverage Information system action for all invocations of this [[order-sign hook](https://cds-hooks.hl7.org/hooks/STU1/order-sign.html)] hook.</t>
+  </si>
+  <si>
+    <t>Use and profiles for [order-select](https://hl7.org/fhir/us/davinci-crd/STU2/hooks.html#order-select) also apply to `order-sign` [([link](https://cds-hooks.hl7.org/hooks/STU1/order-sign.html)) including: the profiles expected to be used for the resources resolved to by the `patientId`are [profile-patient](https://hl7.org/fhir/us/davinci-crd/STU2/StructureDefinition-profile-patient.html)]</t>
+  </si>
+  <si>
+    <t>Use and profiles for [order-select](https://hl7.org/fhir/us/davinci-crd/STU2/hooks.html#order-select) also apply to `order-sign` [([link](https://cds-hooks.hl7.org/hooks/STU1/order-sign.html)) including: the profiles expected to be used for the resources resolved to by the … `encounterId` are [profile-encounter](https://hl7.org/fhir/us/davinci-crd/STU2/StructureDefinition-profile-encounter.html)]</t>
+  </si>
+  <si>
+    <t>Use and profiles for [order-select](https://hl7.org/fhir/us/davinci-crd/STU2/hooks.html#order-select) also apply to `order-sign` [([link](https://cds-hooks.hl7.org/hooks/STU1/order-sign.html)) including: The profiles expected to be used for the resources resolved to by the ... `draftOrders` context element [are] [profile-devicerequest](https://hl7.org/fhir/us/davinci-crd/STU2/StructureDefinition-profile-devicerequest.html), [profile-medicationrequest](https://hl7.org/fhir/us/davinci-crd/STU2/StructureDefinition-profile-medicationrequest.html), [profile-nutritionorder](https://hl7.org/fhir/us/davinci-crd/STU2/StructureDefinition-profile-nutritionorder.html), [profile-visionprescription](https://hl7.org/fhir/us/davinci-crd/STU2/StructureDefinition-profile-visionprescription.html),  [profile-servicerequest](https://hl7.org/fhir/us/davinci-crd/STU2/StructureDefinition-profile-servicerequest.html)]</t>
+  </si>
+  <si>
+    <t>Use and profiles for [order-select](https://hl7.org/fhir/us/davinci-crd/STU2/hooks.html#order-select) also apply to `order-sign` [([link](https://cds-hooks.hl7.org/hooks/STU1/order-sign.html)) including: while this hook does not explicitly list PractitionerRole [([us-core-practitionerrole](http://hl7.org/fhir/us/core/STU3.1.1/StructureDefinition-us-core-practitionerrole.html)) in addition to  [profile-practitioner](https://hl7.org/fhir/us/davinci-crd/STU2/StructureDefinition-profile-practitioner.html)] as an expected resource type for userId, it is not prohibited and is included to allow linking the user to a Practitioner in a specific role acting on behalf of a specific Organization.]</t>
+  </si>
+  <si>
+    <t>[In response to an [encounter-discharge](https://cds-hooks.hl7.org/hooks/encounter-discharge/STU1/encounter-discharge/) hook call, [clients should v]erify that documentation requirements for the services performed have been met to ensure the services provided can be reimbursed</t>
+  </si>
+  <si>
+    <t>[In response to an [encounter-discharge](https://cds-hooks.hl7.org/hooks/encounter-discharge/STU1/encounter-discharge/) hook call, [clients should e]nsure that required follow-up planning is complete and appropriate transfer of care has been arranged, particularly for accountable care models</t>
+  </si>
+  <si>
+    <t>FHIR API</t>
+  </si>
+  <si>
+    <t>User Interaction</t>
+  </si>
+  <si>
+    <t>Registration</t>
+  </si>
+  <si>
+    <t>Prefetch</t>
+  </si>
+  <si>
+    <t>What if</t>
+  </si>
+  <si>
+    <t>CRD Request</t>
+  </si>
+  <si>
+    <t>Logging</t>
+  </si>
+  <si>
+    <t>Security</t>
+  </si>
+  <si>
+    <t>CRD Configuration</t>
+  </si>
+  <si>
+    <t>Resource creation</t>
+  </si>
+  <si>
+    <t>User interaction</t>
+  </si>
+  <si>
+    <t>Deprecated because this is a detail that implementers need to be aware of and handle based on internal implementation choices, but that an external system performing verification won't see or need to check explicitly. 72 is the real requirement.</t>
+  </si>
+  <si>
+    <t>Hook - appointment-book</t>
+  </si>
+  <si>
+    <t>Hook - encounter-start</t>
+  </si>
+  <si>
+    <t>Card - External reference</t>
+  </si>
+  <si>
+    <t>Card - Coverage information</t>
+  </si>
+  <si>
+    <t>Hook - encounter-discharge</t>
+  </si>
+  <si>
+    <t>Card - Identify additional orders</t>
+  </si>
+  <si>
+    <t>Card - Instructions</t>
+  </si>
+  <si>
+    <t>Hook - order-dispatch</t>
+  </si>
+  <si>
+    <t>Hook - order-select</t>
+  </si>
+  <si>
+    <t>Hook - order-sign</t>
+  </si>
+  <si>
+    <t>Card - Propose alternate request</t>
+  </si>
+  <si>
+    <t>Card - Create or update coverage information</t>
+  </si>
+  <si>
+    <t>Card - Request form completion</t>
+  </si>
+  <si>
+    <t>cds-hooks-library_1.0.1@20,24,28,32</t>
+  </si>
+  <si>
+    <t>cds-hooks-library_1.0.1@17-19,21-23,25-27,29-31</t>
+  </si>
+  <si>
+    <t>cds-hooks-library_1.0.1@36,40,44</t>
+  </si>
+  <si>
+    <t>cds-hooks-library_1.0.1@33-35,37-39,41-43</t>
+  </si>
+  <si>
+    <t>cds-hooks-library_1.0.1@48,52,56</t>
+  </si>
+  <si>
+    <t>cds-hooks-library_1.0.1@45-47,49-51,53-55</t>
+  </si>
+  <si>
+    <t>cds-hooks-library_1.0.1@60,64,68,73</t>
+  </si>
+  <si>
+    <t>cds-hooks-library_1.0.1@57-59,61-63,65-67,69-72</t>
+  </si>
+  <si>
+    <t>cds-hooks-library_1.0.1@77,81,85,89,93</t>
+  </si>
+  <si>
+    <t>cds-hooks-library_1.0.1@74-76,78-80,82-84,86-88,90-92</t>
+  </si>
+  <si>
+    <t>cds-hooks-library_1.0.1@4,8,12,16</t>
+  </si>
+  <si>
+    <t>cds-hooks-library_1.0.1@1-3,5-7,9-11,13-15</t>
+  </si>
+  <si>
+    <t>[for the [encounter-discharge](https://cds-hooks.hl7.org/hooks/encounter-discharge/STU1/encounter-discharge/) hook t]he profiles expected to be used for the resources resolved to by the … encounterId … are … [profile-encounter](https://hl7.org/fhir/us/davinci-crd/STU2/StructureDefinition-profile-encounter.html)</t>
+  </si>
+  <si>
+    <t>[for the [encounter-discharge](https://cds-hooks.hl7.org/hooks/encounter-discharge/STU1/encounter-discharge/) hook t]he profiles expected to be used for the resources resolved to by the … patientId … are … [profile-patient](https://hl7.org/fhir/us/davinci-crd/STU2/StructureDefinition-profile-patient.html)</t>
+  </si>
+  <si>
+    <t>[for the [encounter-discharge](https://cds-hooks.hl7.org/hooks/encounter-discharge/STU1/encounter-discharge/) hook t]he profiles expected to be used for the resources resolved to by the userId … are … [profile-practitioner](https://hl7.org/fhir/us/davinci-crd/STU2/StructureDefinition-profile-practitioner.html) [or] [us-core-practitionerrole](http://hl7.org/fhir/us/core/STU3.1.1/StructureDefinition-us-core-practitionerrole.html)</t>
+  </si>
+  <si>
+    <t>[For the enounter-start hook t]he profiles expected to be used for the resources resolved to by the … encounterId … are … [profile-encounter](https://hl7.org/fhir/us/davinci-crd/STU2/StructureDefinition-profile-encounter.html)</t>
+  </si>
+  <si>
+    <t>[For the enounter-start hook t]he profiles expected to be used for the resources resolved to by the … patientId … are … [profile-patient](https://hl7.org/fhir/us/davinci-crd/STU2/StructureDefinition-profile-patient.html)</t>
+  </si>
+  <si>
+    <t>[For the enounter-start hook t]he profiles expected to be used for the resources resolved to by the userId … are … [profile-practitioner](https://hl7.org/fhir/us/davinci-crd/STU2/StructureDefinition-profile-practitioner.html) [or] [us-core-practitionerrole](http://hl7.org/fhir/us/core/STU3.1.1/StructureDefinition-us-core-practitionerrole.html)</t>
+  </si>
+  <si>
+    <t>While this [[appointment-book](https://cds-hooks.hl7.org/hooks/appointment-book/2023SepSTU1Ballot/appointment-book/)] hook supports userIds of Patient and RelatedPerson, for CRD purposes it is enough to support Practitioner and PractitionerRole. [For the appointment-book hook] support for Patient and RelatedPerson as users is optional [([published v1.0 link](https://cds-hooks.hl7.org/hooks/appointment-book/STU1/appointment-book/))]</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[For the appointment-book hook t]he profiles expected to be used for the resources resolved to by the … encounterId … are … </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[profile-encounter]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(https://hl7.org/fhir/us/davinci-crd/STU2/StructureDefinition-profile-encounter.html)</t>
+    </r>
+  </si>
+  <si>
+    <t>[For the appointment-book hook t]he profiles expected to be used for the resources resolved to by the … patientId … are … [profile-patient](https://hl7.org/fhir/us/davinci-crd/STU2/StructureDefinition-profile-patient.html)</t>
+  </si>
+  <si>
+    <t>[For the appointment-book hook t]he profiles expected to be used for the resources resolved to by the userId … are … [profile-practitioner](https://hl7.org/fhir/us/davinci-crd/STU2/StructureDefinition-profile-practitioner.html) [or] [us-core-practitionerrole](http://hl7.org/fhir/us/core/STU3.1.1/StructureDefinition-us-core-practitionerrole.html)</t>
+  </si>
+  <si>
+    <r>
+      <t>[For the appointment-book hook t]he profiles expected to be used for the resources resolved to by the … `appointments` … are …</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[profile-appointment</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>](https://hl7.org/fhir/us/davinci-crd/STU2/StructureDefinition-profile-appointment.html)</t>
+    </r>
+  </si>
+  <si>
+    <t>Deprecated because this is an explanation of what implementers need to do internally to accomplish requirements, for example, adding coverage-information extensions to provided orders (See equirements 278 and 280)</t>
+  </si>
+  <si>
+    <t>https://hl7.org/fhir/us/davinci-crd/STU2/CapabilityStatement-crd-client.html</t>
+  </si>
+  <si>
+    <t>the CRD Client SHALL support all ‘SHOULD’ ‘read’ and ‘search’ capabilities listed below for resources referenced in supported hooks and order types if it does not support returning the associated resources as part of CDS Hooks pre-fetch.</t>
+  </si>
+  <si>
+    <t>Implementations SHALL meet the general security requirements documented in the [HRex implementation guide](http://hl7.org/fhir/us/davinci-hrex/STU1/security.html)</t>
+  </si>
+  <si>
+    <t>https://hl7.org/fhir/us/davinci-crd/STU2/CapabilityStatement-crd-client.html#mode1</t>
+  </si>
+  <si>
+    <t>If the client supports DTR</t>
+  </si>
+  <si>
+    <t>[CRD Clients SHALL also implement the US Core Server Capability Statement imported by this CapabilityStatement]</t>
+  </si>
+  <si>
+    <t>The CRD Client SHALL also support ‘update’ functionality for [the Appointment resource type when] the client allows invoking [the appointment-book hook].</t>
+  </si>
+  <si>
+    <t>The CRD Client SHALL also support ‘update’ functionality for [the Encounter resource type when] the client allows invoking [the encounter-start or encounter-discharge hook].</t>
+  </si>
+  <si>
+    <t>The CRD Client SHALL also support ‘update’ functionality for [the DeviceRequest resource type when] the client allows invoking [the order-dispatch, order-select, or order-sign hook].</t>
+  </si>
+  <si>
+    <t>The CRD Client SHALL also support ‘update’ functionality for [the CommunicationRequest resource type when] the client allows invoking [the order-dispatch, order-select, or order-sign hook].</t>
+  </si>
+  <si>
+    <t>The CRD Client SHALL also support ‘update’ functionality for [the MedicationRequest resource type when] the client allows invoking [the order-dispatch, order-select, or order-sign hook].</t>
+  </si>
+  <si>
+    <t>The CRD Client SHALL also support ‘update’ functionality for [the NutritionOrder resource type when] the client allows invoking [the order-dispatch, order-select, or order-sign hook].</t>
+  </si>
+  <si>
+    <t>The CRD Client SHALL also support ‘update’ functionality for [the ServiceRequest resource type when] the client allows invoking [the order-dispatch, order-select, or order-sign hook].</t>
+  </si>
+  <si>
+    <t>The CRD Client SHALL also support ‘update’ functionality for [the VisionPrescription resource type when] the client allows invoking [the order-dispatch, order-select, or order-sign hook].</t>
+  </si>
+  <si>
+    <t>This only adds a few capabilities beyond what is already in US Core starting with 3.1.1:
+- Coverage search doesn't get required by US Core until US Core 6
+- Coverage search by status not required by US Core
+- Encounter search by location (with patient) required by US Core starting in US Core 5
+- PractitionerRole search by organization and id not required by US Core</t>
+  </si>
+  <si>
+    <t>When a CRD client invokes a CRD server via CDS Hooks, it will provide an access token that allows the CRD server to retrieve additional patient information.</t>
   </si>
 </sst>
 </file>
@@ -3453,6 +3622,20 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -3471,20 +3654,6 @@
     <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -3850,14 +4019,14 @@
       <c r="C3" s="14"/>
     </row>
     <row r="4" spans="1:3" ht="409" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="35" t="s">
-        <v>442</v>
+      <c r="A4" s="43" t="s">
+        <v>410</v>
       </c>
       <c r="B4" s="15"/>
       <c r="C4" s="16"/>
     </row>
     <row r="5" spans="1:3" ht="258" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="36"/>
+      <c r="A5" s="44"/>
       <c r="B5" s="19"/>
       <c r="C5" s="14"/>
     </row>
@@ -3869,17 +4038,17 @@
       <c r="C6" s="11"/>
     </row>
     <row r="7" spans="1:3" ht="98" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="37" t="s">
+      <c r="A7" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="38"/>
+      <c r="B7" s="46"/>
     </row>
     <row r="8" spans="1:3" ht="126" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="37"/>
-      <c r="B8" s="39"/>
+      <c r="A8" s="45"/>
+      <c r="B8" s="47"/>
     </row>
     <row r="9" spans="1:3" ht="68" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="35"/>
+      <c r="A9" s="43"/>
       <c r="B9" s="18"/>
     </row>
     <row r="10" spans="1:3" ht="292" x14ac:dyDescent="0.2">
@@ -3902,7 +4071,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0272D98A-080C-3945-A7E0-CB54FB3A65A9}">
-  <dimension ref="A1:AE434"/>
+  <dimension ref="A1:AE433"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="25"/>
@@ -3928,68 +4097,68 @@
     <col min="22" max="16384" width="10.83203125" style="29"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" s="47" customFormat="1" ht="32" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+    <row r="1" spans="1:31" s="41" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+      <c r="A1" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="41" t="s">
+      <c r="B1" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="42" t="s">
+      <c r="C1" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="41" t="s">
+      <c r="D1" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="41" t="s">
-        <v>443</v>
-      </c>
-      <c r="F1" s="42" t="s">
+      <c r="E1" s="35" t="s">
+        <v>411</v>
+      </c>
+      <c r="F1" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="41" t="s">
+      <c r="G1" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="43" t="s">
+      <c r="H1" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="I1" s="44" t="s">
+      <c r="I1" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="44" t="s">
+      <c r="J1" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="K1" s="44" t="s">
+      <c r="K1" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="L1" s="44" t="s">
+      <c r="L1" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="M1" s="45" t="s">
+      <c r="M1" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="N1" s="45" t="s">
+      <c r="N1" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="O1" s="46" t="s">
+      <c r="O1" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="P1" s="46" t="s">
+      <c r="P1" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="Q1" s="43" t="s">
+      <c r="Q1" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="R1" s="46" t="s">
+      <c r="R1" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="S1" s="46" t="s">
+      <c r="S1" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="T1" s="43" t="s">
+      <c r="T1" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="Y1" s="48"/>
+      <c r="Y1" s="42"/>
     </row>
     <row r="2" spans="1:31" s="24" customFormat="1" ht="85" x14ac:dyDescent="0.2">
       <c r="A2" s="25">
@@ -4052,6 +4221,9 @@
       <c r="N3" s="30" t="s">
         <v>35</v>
       </c>
+      <c r="P3" s="27" t="s">
+        <v>440</v>
+      </c>
       <c r="T3" s="27" t="s">
         <v>36</v>
       </c>
@@ -4350,10 +4522,10 @@
         <v>41</v>
       </c>
       <c r="T16" s="27" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A17" s="25">
         <v>16</v>
       </c>
@@ -4373,7 +4545,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="85" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A18" s="25">
         <v>17</v>
       </c>
@@ -4397,7 +4569,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="85" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A19" s="25">
         <v>18</v>
       </c>
@@ -4417,7 +4589,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="85" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A20" s="25">
         <v>19</v>
       </c>
@@ -4437,7 +4609,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="85" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A21" s="25">
         <v>20</v>
       </c>
@@ -4461,7 +4633,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="85" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:16" ht="102" x14ac:dyDescent="0.2">
       <c r="A22" s="25">
         <v>21</v>
       </c>
@@ -4476,6 +4648,12 @@
       </c>
       <c r="E22" s="25" t="s">
         <v>34</v>
+      </c>
+      <c r="G22" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="H22" s="27" t="s">
+        <v>418</v>
       </c>
       <c r="M22" s="30" t="str" cm="1">
         <f t="array" ref="M22">PAGE_NAME(B22)</f>
@@ -4484,8 +4662,11 @@
       <c r="N22" s="30" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="23" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+      <c r="P22" s="27" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A23" s="25">
         <v>22</v>
       </c>
@@ -4505,7 +4686,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="102" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:16" ht="102" x14ac:dyDescent="0.2">
       <c r="A24" s="25">
         <v>23</v>
       </c>
@@ -4529,7 +4710,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="102" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:16" ht="102" x14ac:dyDescent="0.2">
       <c r="A25" s="25">
         <v>24</v>
       </c>
@@ -4553,7 +4734,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="119" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:16" ht="119" x14ac:dyDescent="0.2">
       <c r="A26" s="25">
         <v>25</v>
       </c>
@@ -4577,7 +4758,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A27" s="25">
         <v>26</v>
       </c>
@@ -4601,7 +4782,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A28" s="25">
         <v>27</v>
       </c>
@@ -4625,7 +4806,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="119" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:16" ht="119" x14ac:dyDescent="0.2">
       <c r="A29" s="25">
         <v>28</v>
       </c>
@@ -4649,7 +4830,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A30" s="25">
         <v>29</v>
       </c>
@@ -4673,7 +4854,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="102" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:16" ht="102" x14ac:dyDescent="0.2">
       <c r="A31" s="25">
         <v>30</v>
       </c>
@@ -4696,8 +4877,11 @@
       <c r="N31" s="30" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="32" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+      <c r="P31" s="27" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A32" s="25">
         <v>31</v>
       </c>
@@ -4720,8 +4904,11 @@
       <c r="N32" s="30" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="33" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+      <c r="P32" s="27" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A33" s="25">
         <v>32</v>
       </c>
@@ -4744,8 +4931,11 @@
       <c r="N33" s="30" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="34" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+      <c r="P33" s="27" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A34" s="25">
         <v>33</v>
       </c>
@@ -4768,8 +4958,11 @@
       <c r="N34" s="30" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="35" spans="1:14" ht="85" x14ac:dyDescent="0.2">
+      <c r="P34" s="27" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A35" s="25">
         <v>34</v>
       </c>
@@ -4789,7 +4982,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="36" spans="1:14" ht="102" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:16" ht="102" x14ac:dyDescent="0.2">
       <c r="A36" s="25">
         <v>35</v>
       </c>
@@ -4809,7 +5002,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="37" spans="1:14" ht="85" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A37" s="25">
         <v>36</v>
       </c>
@@ -4829,7 +5022,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="38" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A38" s="25">
         <v>37</v>
       </c>
@@ -4849,7 +5042,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="39" spans="1:14" ht="102" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:16" ht="102" x14ac:dyDescent="0.2">
       <c r="A39" s="25">
         <v>38</v>
       </c>
@@ -4869,7 +5062,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="40" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A40" s="25">
         <v>39</v>
       </c>
@@ -4877,7 +5070,7 @@
         <v>87</v>
       </c>
       <c r="C40" s="25" t="s">
-        <v>441</v>
+        <v>409</v>
       </c>
       <c r="D40" s="25" t="s">
         <v>50</v>
@@ -4893,7 +5086,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="41" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A41" s="25">
         <v>40</v>
       </c>
@@ -4917,7 +5110,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="42" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A42" s="25">
         <v>41</v>
       </c>
@@ -4941,7 +5134,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="43" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A43" s="25">
         <v>42</v>
       </c>
@@ -4961,7 +5154,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="44" spans="1:14" ht="221" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:16" ht="221" x14ac:dyDescent="0.2">
       <c r="A44" s="25">
         <v>43</v>
       </c>
@@ -4984,8 +5177,11 @@
       <c r="N44" s="30" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="45" spans="1:14" ht="119" x14ac:dyDescent="0.2">
+      <c r="P44" s="27" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" ht="119" x14ac:dyDescent="0.2">
       <c r="A45" s="25">
         <v>44</v>
       </c>
@@ -5009,7 +5205,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="46" spans="1:14" ht="170" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:16" ht="170" x14ac:dyDescent="0.2">
       <c r="A46" s="25">
         <v>45</v>
       </c>
@@ -5033,7 +5229,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="47" spans="1:14" ht="34" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:16" ht="34" x14ac:dyDescent="0.2">
       <c r="A47" s="25">
         <v>46</v>
       </c>
@@ -5057,7 +5253,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="48" spans="1:14" ht="187" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:16" ht="187" x14ac:dyDescent="0.2">
       <c r="A48" s="25">
         <v>47</v>
       </c>
@@ -5248,6 +5444,9 @@
       <c r="N55" s="30" t="s">
         <v>95</v>
       </c>
+      <c r="P55" s="27" t="s">
+        <v>443</v>
+      </c>
     </row>
     <row r="56" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="25">
@@ -5297,7 +5496,7 @@
         <v>110</v>
       </c>
       <c r="T57" s="27" t="s">
-        <v>446</v>
+        <v>414</v>
       </c>
     </row>
     <row r="58" spans="1:20" ht="119" x14ac:dyDescent="0.2">
@@ -5464,7 +5663,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="65" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:20" ht="68" x14ac:dyDescent="0.2">
       <c r="A65" s="25">
         <v>64</v>
       </c>
@@ -5483,8 +5682,11 @@
       <c r="N65" s="30" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="66" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+      <c r="P65" s="27" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="66" spans="1:20" ht="68" x14ac:dyDescent="0.2">
       <c r="A66" s="25">
         <v>65</v>
       </c>
@@ -5503,8 +5705,11 @@
       <c r="N66" s="30" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="67" spans="1:14" ht="85" x14ac:dyDescent="0.2">
+      <c r="P66" s="27" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="67" spans="1:20" ht="85" x14ac:dyDescent="0.2">
       <c r="A67" s="25">
         <v>66</v>
       </c>
@@ -5523,8 +5728,11 @@
       <c r="N67" s="30" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="68" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+      <c r="P67" s="27" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="68" spans="1:20" ht="68" x14ac:dyDescent="0.2">
       <c r="A68" s="25">
         <v>67</v>
       </c>
@@ -5548,7 +5756,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="69" spans="1:14" ht="34" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:20" ht="34" x14ac:dyDescent="0.2">
       <c r="A69" s="25">
         <v>68</v>
       </c>
@@ -5572,7 +5780,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="70" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:20" ht="51" x14ac:dyDescent="0.2">
       <c r="A70" s="25">
         <v>69</v>
       </c>
@@ -5591,8 +5799,11 @@
       <c r="N70" s="30" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="71" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+      <c r="P70" s="27" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="71" spans="1:20" ht="51" x14ac:dyDescent="0.2">
       <c r="A71" s="25">
         <v>70</v>
       </c>
@@ -5612,7 +5823,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="72" spans="1:14" ht="34" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:20" ht="34" x14ac:dyDescent="0.2">
       <c r="A72" s="25">
         <v>71</v>
       </c>
@@ -5635,8 +5846,11 @@
       <c r="N72" s="30" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="73" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+      <c r="P72" s="27" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="73" spans="1:20" ht="68" x14ac:dyDescent="0.2">
       <c r="A73" s="25">
         <v>72</v>
       </c>
@@ -5655,8 +5869,11 @@
       <c r="N73" s="30" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="74" spans="1:14" ht="102" x14ac:dyDescent="0.2">
+      <c r="P73" s="27" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="74" spans="1:20" ht="102" x14ac:dyDescent="0.2">
       <c r="A74" s="25">
         <v>73</v>
       </c>
@@ -5667,7 +5884,7 @@
         <v>134</v>
       </c>
       <c r="D74" s="25" t="s">
-        <v>33</v>
+        <v>206</v>
       </c>
       <c r="E74" s="25" t="s">
         <v>34</v>
@@ -5679,8 +5896,14 @@
       <c r="N74" s="30" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="75" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+      <c r="P74" s="27" t="s">
+        <v>445</v>
+      </c>
+      <c r="T74" s="27" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="75" spans="1:20" ht="102" x14ac:dyDescent="0.2">
       <c r="A75" s="25">
         <v>74</v>
       </c>
@@ -5691,13 +5914,19 @@
         <v>135</v>
       </c>
       <c r="D75" s="25" t="s">
-        <v>33</v>
+        <v>206</v>
       </c>
       <c r="E75" s="25" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="76" spans="1:14" ht="136" x14ac:dyDescent="0.2">
+      <c r="P75" s="27" t="s">
+        <v>445</v>
+      </c>
+      <c r="T75" s="27" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="76" spans="1:20" ht="136" x14ac:dyDescent="0.2">
       <c r="A76" s="25">
         <v>75</v>
       </c>
@@ -5720,8 +5949,11 @@
       <c r="N76" s="30" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="77" spans="1:14" ht="136" x14ac:dyDescent="0.2">
+      <c r="P76" s="27" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="77" spans="1:20" ht="136" x14ac:dyDescent="0.2">
       <c r="A77" s="25">
         <v>76</v>
       </c>
@@ -5745,7 +5977,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="78" spans="1:14" ht="34" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:20" ht="34" x14ac:dyDescent="0.2">
       <c r="A78" s="25">
         <v>77</v>
       </c>
@@ -5765,7 +5997,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="79" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:20" ht="68" x14ac:dyDescent="0.2">
       <c r="A79" s="25">
         <v>78</v>
       </c>
@@ -5784,8 +6016,11 @@
       <c r="N79" s="30" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="80" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+      <c r="P79" s="27" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="80" spans="1:20" ht="51" x14ac:dyDescent="0.2">
       <c r="A80" s="25">
         <v>79</v>
       </c>
@@ -5808,6 +6043,9 @@
       <c r="N80" s="30" t="s">
         <v>132</v>
       </c>
+      <c r="P80" s="27" t="s">
+        <v>446</v>
+      </c>
     </row>
     <row r="81" spans="1:20" ht="51" x14ac:dyDescent="0.2">
       <c r="A81" s="25">
@@ -5832,6 +6070,9 @@
       <c r="N81" s="30" t="s">
         <v>132</v>
       </c>
+      <c r="P81" s="27" t="s">
+        <v>446</v>
+      </c>
     </row>
     <row r="82" spans="1:20" ht="51" x14ac:dyDescent="0.2">
       <c r="A82" s="25">
@@ -5905,6 +6146,9 @@
         <f t="array" ref="N84">SECTION_NAME(B84)</f>
         <v>privacy-security-and-safety</v>
       </c>
+      <c r="P84" s="27" t="s">
+        <v>447</v>
+      </c>
     </row>
     <row r="85" spans="1:20" ht="51" x14ac:dyDescent="0.2">
       <c r="A85" s="25">
@@ -5922,6 +6166,9 @@
       <c r="E85" s="25" t="s">
         <v>29</v>
       </c>
+      <c r="P85" s="27" t="s">
+        <v>447</v>
+      </c>
     </row>
     <row r="86" spans="1:20" ht="68" x14ac:dyDescent="0.2">
       <c r="A86" s="25">
@@ -5939,6 +6186,9 @@
       <c r="E86" s="25" t="s">
         <v>29</v>
       </c>
+      <c r="P86" s="27" t="s">
+        <v>447</v>
+      </c>
     </row>
     <row r="87" spans="1:20" ht="68" x14ac:dyDescent="0.2">
       <c r="A87" s="25">
@@ -5964,8 +6214,11 @@
         <f t="array" ref="N87">SECTION_NAME(B87)</f>
         <v>privacy-security-and-safety</v>
       </c>
+      <c r="P87" s="27" t="s">
+        <v>447</v>
+      </c>
       <c r="T87" s="27" t="s">
-        <v>440</v>
+        <v>408</v>
       </c>
     </row>
     <row r="88" spans="1:20" ht="51" x14ac:dyDescent="0.2">
@@ -5992,6 +6245,9 @@
         <f t="array" ref="N88">SECTION_NAME(B88)</f>
         <v>privacy-security-and-safety</v>
       </c>
+      <c r="P88" s="27" t="s">
+        <v>447</v>
+      </c>
     </row>
     <row r="89" spans="1:20" ht="51" x14ac:dyDescent="0.2">
       <c r="A89" s="25">
@@ -6017,6 +6273,9 @@
         <f t="array" ref="N89">SECTION_NAME(B89)</f>
         <v>privacy-security-and-safety</v>
       </c>
+      <c r="P89" s="27" t="s">
+        <v>447</v>
+      </c>
     </row>
     <row r="90" spans="1:20" ht="34" x14ac:dyDescent="0.2">
       <c r="A90" s="25">
@@ -6042,6 +6301,9 @@
         <f t="array" ref="N90">SECTION_NAME(B90)</f>
         <v>privacy-security-and-safety</v>
       </c>
+      <c r="P90" s="27" t="s">
+        <v>447</v>
+      </c>
     </row>
     <row r="91" spans="1:20" ht="34" x14ac:dyDescent="0.2">
       <c r="A91" s="25">
@@ -6093,7 +6355,7 @@
         <v>privacy-security-and-safety</v>
       </c>
       <c r="T92" s="27" t="s">
-        <v>440</v>
+        <v>408</v>
       </c>
     </row>
     <row r="93" spans="1:20" ht="68" x14ac:dyDescent="0.2">
@@ -6120,6 +6382,9 @@
         <f t="array" ref="N93">SECTION_NAME(B93)</f>
         <v>privacy-security-and-safety</v>
       </c>
+      <c r="P93" s="27" t="s">
+        <v>447</v>
+      </c>
     </row>
     <row r="94" spans="1:20" ht="34" x14ac:dyDescent="0.2">
       <c r="A94" s="25">
@@ -6262,6 +6527,9 @@
         <f t="array" ref="N99">SECTION_NAME(B99)</f>
         <v>privacy-security-and-safety</v>
       </c>
+      <c r="P99" s="27" t="s">
+        <v>447</v>
+      </c>
     </row>
     <row r="100" spans="1:20" ht="68" x14ac:dyDescent="0.2">
       <c r="A100" s="25">
@@ -6312,8 +6580,11 @@
         <f t="array" ref="N101">SECTION_NAME(B101)</f>
         <v>privacy-security-and-safety</v>
       </c>
+      <c r="P101" s="27" t="s">
+        <v>447</v>
+      </c>
       <c r="T101" s="27" t="s">
-        <v>440</v>
+        <v>408</v>
       </c>
     </row>
     <row r="102" spans="1:20" ht="51" x14ac:dyDescent="0.2">
@@ -6591,7 +6862,7 @@
         <v>configuration-options-extension</v>
       </c>
     </row>
-    <row r="113" spans="1:14" ht="85" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A113" s="25">
         <v>112</v>
       </c>
@@ -6616,7 +6887,7 @@
         <v>configuration-options-extension</v>
       </c>
     </row>
-    <row r="114" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A114" s="25">
         <v>113</v>
       </c>
@@ -6641,7 +6912,7 @@
         <v>configuration-options-extension</v>
       </c>
     </row>
-    <row r="115" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A115" s="25">
         <v>114</v>
       </c>
@@ -6666,7 +6937,7 @@
         <v>configuration-options-extension</v>
       </c>
     </row>
-    <row r="116" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A116" s="25">
         <v>115</v>
       </c>
@@ -6691,7 +6962,7 @@
         <v>configuration-options-extension</v>
       </c>
     </row>
-    <row r="117" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A117" s="25">
         <v>116</v>
       </c>
@@ -6716,7 +6987,7 @@
         <v>configuration-options-extension</v>
       </c>
     </row>
-    <row r="118" spans="1:14" ht="85" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A118" s="25">
         <v>117</v>
       </c>
@@ -6741,7 +7012,7 @@
         <v>configuration-options-extension</v>
       </c>
     </row>
-    <row r="119" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A119" s="25">
         <v>118</v>
       </c>
@@ -6766,7 +7037,7 @@
         <v>configuration-options-extension</v>
       </c>
     </row>
-    <row r="120" spans="1:14" ht="102" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:16" ht="102" x14ac:dyDescent="0.2">
       <c r="A120" s="25">
         <v>119</v>
       </c>
@@ -6791,7 +7062,7 @@
         <v>configuration-options-extension</v>
       </c>
     </row>
-    <row r="121" spans="1:14" ht="34" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:16" ht="34" x14ac:dyDescent="0.2">
       <c r="A121" s="25">
         <v>120</v>
       </c>
@@ -6816,7 +7087,7 @@
         <v>configuration-options-extension</v>
       </c>
     </row>
-    <row r="122" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A122" s="25">
         <v>121</v>
       </c>
@@ -6841,7 +7112,7 @@
         <v>configuration-options-extension</v>
       </c>
     </row>
-    <row r="123" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A123" s="25">
         <v>122</v>
       </c>
@@ -6866,7 +7137,7 @@
         <v>configuration-options-extension</v>
       </c>
     </row>
-    <row r="124" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A124" s="25">
         <v>123</v>
       </c>
@@ -6891,7 +7162,7 @@
         <v>configuration-options-extension</v>
       </c>
     </row>
-    <row r="125" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A125" s="25">
         <v>124</v>
       </c>
@@ -6916,7 +7187,7 @@
         <v>configuration-options-extension</v>
       </c>
     </row>
-    <row r="126" spans="1:14" ht="85" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A126" s="25">
         <v>125</v>
       </c>
@@ -6941,7 +7212,7 @@
         <v>hook-configuration-extension</v>
       </c>
     </row>
-    <row r="127" spans="1:14" ht="119" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:16" ht="119" x14ac:dyDescent="0.2">
       <c r="A127" s="25">
         <v>126</v>
       </c>
@@ -6965,8 +7236,11 @@
         <f t="array" ref="N127">SECTION_NAME(B127)</f>
         <v>hook-configuration-extension</v>
       </c>
-    </row>
-    <row r="128" spans="1:14" ht="85" x14ac:dyDescent="0.2">
+      <c r="P127" s="27" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="128" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A128" s="25">
         <v>127</v>
       </c>
@@ -7091,7 +7365,7 @@
         <v>hook-configuration-extension</v>
       </c>
     </row>
-    <row r="133" spans="1:20" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:20" ht="409.5" x14ac:dyDescent="0.2">
       <c r="A133" s="25">
         <v>132</v>
       </c>
@@ -7115,8 +7389,11 @@
         <f t="array" ref="N133">SECTION_NAME(B133)</f>
         <v>additional-prefetch-capabilities</v>
       </c>
+      <c r="P133" s="27" t="s">
+        <v>443</v>
+      </c>
       <c r="T133" s="27" t="s">
-        <v>447</v>
+        <v>415</v>
       </c>
     </row>
     <row r="134" spans="1:20" ht="68" x14ac:dyDescent="0.2">
@@ -7143,6 +7420,9 @@
         <f t="array" ref="N134">SECTION_NAME(B134)</f>
         <v>additional-prefetch-capabilities</v>
       </c>
+      <c r="P134" s="27" t="s">
+        <v>443</v>
+      </c>
     </row>
     <row r="135" spans="1:20" ht="68" x14ac:dyDescent="0.2">
       <c r="A135" s="25">
@@ -7169,7 +7449,7 @@
         <v>additional-response-capabilities</v>
       </c>
       <c r="T135" s="27" t="s">
-        <v>449</v>
+        <v>417</v>
       </c>
     </row>
     <row r="136" spans="1:20" ht="51" x14ac:dyDescent="0.2">
@@ -7238,6 +7518,9 @@
         <f t="array" ref="N138">SECTION_NAME(B138)</f>
         <v>linkage-between-created-resources</v>
       </c>
+      <c r="P138" s="27" t="s">
+        <v>449</v>
+      </c>
     </row>
     <row r="139" spans="1:20" ht="85" x14ac:dyDescent="0.2">
       <c r="A139" s="25">
@@ -7263,6 +7546,9 @@
         <f t="array" ref="N139">SECTION_NAME(B139)</f>
         <v>linkage-between-created-resources</v>
       </c>
+      <c r="P139" s="27" t="s">
+        <v>449</v>
+      </c>
     </row>
     <row r="140" spans="1:20" ht="51" x14ac:dyDescent="0.2">
       <c r="A140" s="25">
@@ -7288,6 +7574,9 @@
         <f t="array" ref="N140">SECTION_NAME(B140)</f>
         <v>linkage-between-created-resources</v>
       </c>
+      <c r="P140" s="27" t="s">
+        <v>449</v>
+      </c>
     </row>
     <row r="141" spans="1:20" ht="85" x14ac:dyDescent="0.2">
       <c r="A141" s="25">
@@ -7363,6 +7652,9 @@
         <f t="array" ref="N143">SECTION_NAME(B143)</f>
         <v>controlling-hook-invocation</v>
       </c>
+      <c r="P143" s="27" t="s">
+        <v>445</v>
+      </c>
     </row>
     <row r="144" spans="1:20" ht="51" x14ac:dyDescent="0.2">
       <c r="A144" s="25">
@@ -7413,6 +7705,9 @@
         <f t="array" ref="N145">SECTION_NAME(B145)</f>
         <v>controlling-hook-invocation</v>
       </c>
+      <c r="P145" s="27" t="s">
+        <v>445</v>
+      </c>
     </row>
     <row r="146" spans="1:20" ht="51" x14ac:dyDescent="0.2">
       <c r="A146" s="25">
@@ -7438,6 +7733,9 @@
         <f t="array" ref="N146">SECTION_NAME(B146)</f>
         <v>controlling-hook-invocation</v>
       </c>
+      <c r="P146" s="27" t="s">
+        <v>445</v>
+      </c>
     </row>
     <row r="147" spans="1:20" ht="85" x14ac:dyDescent="0.2">
       <c r="A147" s="25">
@@ -7463,6 +7761,9 @@
         <f t="array" ref="N147">SECTION_NAME(B147)</f>
         <v>controlling-hook-invocation</v>
       </c>
+      <c r="P147" s="27" t="s">
+        <v>445</v>
+      </c>
     </row>
     <row r="148" spans="1:20" ht="34" x14ac:dyDescent="0.2">
       <c r="A148" s="25">
@@ -7513,6 +7814,9 @@
         <f t="array" ref="N149">SECTION_NAME(B149)</f>
         <v>supported-hooks</v>
       </c>
+      <c r="P149" s="27" t="s">
+        <v>445</v>
+      </c>
     </row>
     <row r="150" spans="1:20" ht="68" x14ac:dyDescent="0.2">
       <c r="A150" s="25">
@@ -7538,6 +7842,9 @@
         <f t="array" ref="N150">SECTION_NAME(B150)</f>
         <v>supported-hooks</v>
       </c>
+      <c r="P150" s="27" t="s">
+        <v>445</v>
+      </c>
     </row>
     <row r="151" spans="1:20" ht="407" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="25">
@@ -7563,6 +7870,9 @@
         <f t="array" ref="N151">SECTION_NAME(B151)</f>
         <v>supported-hooks</v>
       </c>
+      <c r="P151" s="27" t="s">
+        <v>445</v>
+      </c>
       <c r="T151" s="27" t="s">
         <v>228</v>
       </c>
@@ -7792,7 +8102,7 @@
         <v>supported-hooks</v>
       </c>
     </row>
-    <row r="161" spans="1:14" ht="85" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A161" s="25">
         <v>160</v>
       </c>
@@ -7817,7 +8127,7 @@
         <v>supported-hooks</v>
       </c>
     </row>
-    <row r="162" spans="1:14" ht="85" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A162" s="25">
         <v>161</v>
       </c>
@@ -7842,7 +8152,7 @@
         <v>supported-hooks</v>
       </c>
     </row>
-    <row r="163" spans="1:14" ht="119" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:16" ht="119" x14ac:dyDescent="0.2">
       <c r="A163" s="25">
         <v>162</v>
       </c>
@@ -7867,7 +8177,7 @@
         <v>supported-hooks</v>
       </c>
     </row>
-    <row r="164" spans="1:14" ht="119" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:16" ht="119" x14ac:dyDescent="0.2">
       <c r="A164" s="25">
         <v>163</v>
       </c>
@@ -7892,7 +8202,7 @@
         <v>supported-hooks</v>
       </c>
     </row>
-    <row r="165" spans="1:14" ht="221" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:16" ht="221" x14ac:dyDescent="0.2">
       <c r="A165" s="25">
         <v>164</v>
       </c>
@@ -7913,7 +8223,7 @@
         <v>hook-categories</v>
       </c>
     </row>
-    <row r="166" spans="1:14" ht="136" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:16" ht="136" x14ac:dyDescent="0.2">
       <c r="A166" s="25">
         <v>165</v>
       </c>
@@ -7934,7 +8244,7 @@
         <v>hook-categories</v>
       </c>
     </row>
-    <row r="167" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A167" s="25">
         <v>166</v>
       </c>
@@ -7955,7 +8265,7 @@
         <v>hook-categories</v>
       </c>
     </row>
-    <row r="168" spans="1:14" ht="255" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:16" ht="255" x14ac:dyDescent="0.2">
       <c r="A168" s="25">
         <v>167</v>
       </c>
@@ -7963,7 +8273,7 @@
         <v>242</v>
       </c>
       <c r="C168" s="25" t="s">
-        <v>439</v>
+        <v>407</v>
       </c>
       <c r="D168" s="25" t="s">
         <v>157</v>
@@ -7976,7 +8286,7 @@
         <v>hook-categories</v>
       </c>
     </row>
-    <row r="169" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A169" s="25">
         <v>168</v>
       </c>
@@ -7997,7 +8307,7 @@
         <v>hook-categories</v>
       </c>
     </row>
-    <row r="170" spans="1:14" ht="34" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:16" ht="34" x14ac:dyDescent="0.2">
       <c r="A170" s="25">
         <v>169</v>
       </c>
@@ -8022,7 +8332,7 @@
         <v>appointment-book</v>
       </c>
     </row>
-    <row r="171" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A171" s="25">
         <v>170</v>
       </c>
@@ -8037,13 +8347,16 @@
       </c>
       <c r="E171" s="25" t="s">
         <v>38</v>
+      </c>
+      <c r="F171" s="25" t="s">
+        <v>465</v>
       </c>
       <c r="N171" s="30" t="str" cm="1">
         <f t="array" ref="N171">SECTION_NAME(B172)</f>
         <v>appointment-book</v>
       </c>
     </row>
-    <row r="172" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A172" s="25">
         <v>171</v>
       </c>
@@ -8058,13 +8371,19 @@
       </c>
       <c r="E172" s="25" t="s">
         <v>34</v>
+      </c>
+      <c r="F172" s="25" t="s">
+        <v>466</v>
       </c>
       <c r="N172" s="30" t="str" cm="1">
         <f t="array" ref="N172">SECTION_NAME(B173)</f>
         <v>appointment-book</v>
       </c>
-    </row>
-    <row r="173" spans="1:14" ht="136" x14ac:dyDescent="0.2">
+      <c r="P172" s="27" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="173" spans="1:16" ht="136" x14ac:dyDescent="0.2">
       <c r="A173" s="25">
         <v>172</v>
       </c>
@@ -8084,8 +8403,11 @@
         <f t="array" ref="N173">SECTION_NAME(B174)</f>
         <v>appointment-book</v>
       </c>
-    </row>
-    <row r="174" spans="1:14" ht="85" x14ac:dyDescent="0.2">
+      <c r="P173" s="27" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="174" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A174" s="25">
         <v>173</v>
       </c>
@@ -8106,7 +8428,7 @@
         <v>appointment-book</v>
       </c>
     </row>
-    <row r="175" spans="1:14" ht="102" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:16" ht="102" x14ac:dyDescent="0.2">
       <c r="A175" s="25">
         <v>174</v>
       </c>
@@ -8127,7 +8449,7 @@
         <v>appointment-book</v>
       </c>
     </row>
-    <row r="176" spans="1:14" ht="102" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:16" ht="102" x14ac:dyDescent="0.2">
       <c r="A176" s="25">
         <v>175</v>
       </c>
@@ -8177,10 +8499,10 @@
         <v>248</v>
       </c>
       <c r="C178" s="25" t="s">
-        <v>256</v>
+        <v>486</v>
       </c>
       <c r="D178" s="25" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="E178" s="25" t="s">
         <v>34</v>
@@ -8189,6 +8511,9 @@
         <f t="array" ref="N178">SECTION_NAME(B179)</f>
         <v>appointment-book</v>
       </c>
+      <c r="P178" s="27" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="179" spans="1:21" ht="68" x14ac:dyDescent="0.2">
       <c r="A179" s="25">
@@ -8198,10 +8523,10 @@
         <v>248</v>
       </c>
       <c r="C179" s="25" t="s">
-        <v>257</v>
+        <v>485</v>
       </c>
       <c r="D179" s="25" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="E179" s="25" t="s">
         <v>34</v>
@@ -8210,6 +8535,9 @@
         <f t="array" ref="N179">SECTION_NAME(B180)</f>
         <v>appointment-book</v>
       </c>
+      <c r="P179" s="27" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="180" spans="1:21" ht="68" x14ac:dyDescent="0.2">
       <c r="A180" s="25">
@@ -8219,10 +8547,10 @@
         <v>248</v>
       </c>
       <c r="C180" s="25" t="s">
-        <v>258</v>
+        <v>484</v>
       </c>
       <c r="D180" s="25" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="E180" s="25" t="s">
         <v>34</v>
@@ -8231,6 +8559,9 @@
         <f t="array" ref="N180">SECTION_NAME(B181)</f>
         <v>appointment-book</v>
       </c>
+      <c r="P180" s="27" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="181" spans="1:21" ht="68" x14ac:dyDescent="0.2">
       <c r="A181" s="25">
@@ -8240,10 +8571,10 @@
         <v>248</v>
       </c>
       <c r="C181" s="25" t="s">
-        <v>259</v>
+        <v>487</v>
       </c>
       <c r="D181" s="25" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="E181" s="25" t="s">
         <v>34</v>
@@ -8252,6 +8583,9 @@
         <f t="array" ref="N181">SECTION_NAME(B182)</f>
         <v>appointment-book</v>
       </c>
+      <c r="P181" s="27" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="182" spans="1:21" ht="153" x14ac:dyDescent="0.2">
       <c r="A182" s="25">
@@ -8261,7 +8595,7 @@
         <v>248</v>
       </c>
       <c r="C182" s="25" t="s">
-        <v>260</v>
+        <v>483</v>
       </c>
       <c r="D182" s="25" t="s">
         <v>28</v>
@@ -8286,7 +8620,7 @@
         <v>248</v>
       </c>
       <c r="C183" s="25" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="D183" s="25" t="s">
         <v>28</v>
@@ -8311,7 +8645,7 @@
         <v>248</v>
       </c>
       <c r="C184" s="25" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="D184" s="25" t="s">
         <v>33</v>
@@ -8327,6 +8661,9 @@
         <f t="array" ref="N184">SECTION_NAME(B184)</f>
         <v>appointment-book</v>
       </c>
+      <c r="P184" s="27" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="185" spans="1:21" ht="102" x14ac:dyDescent="0.2">
       <c r="A185" s="25">
@@ -8336,7 +8673,7 @@
         <v>248</v>
       </c>
       <c r="C185" s="25" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="D185" s="25" t="s">
         <v>33</v>
@@ -8358,16 +8695,19 @@
         <v>185</v>
       </c>
       <c r="B186" s="33" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="C186" s="25" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="D186" s="25" t="s">
         <v>33</v>
       </c>
       <c r="E186" s="25" t="s">
         <v>38</v>
+      </c>
+      <c r="F186" s="25" t="s">
+        <v>467</v>
       </c>
       <c r="N186" s="30" t="str" cm="1">
         <f t="array" ref="N186">SECTION_NAME(B186)</f>
@@ -8380,31 +8720,37 @@
         <v>186</v>
       </c>
       <c r="B187" s="33" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="C187" s="25" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="D187" s="25" t="s">
         <v>33</v>
       </c>
       <c r="E187" s="25" t="s">
         <v>34</v>
+      </c>
+      <c r="F187" s="25" t="s">
+        <v>468</v>
       </c>
       <c r="N187" s="30" t="str" cm="1">
         <f t="array" ref="N187">SECTION_NAME(B187)</f>
         <v>encounter-start</v>
       </c>
+      <c r="P187" s="27" t="s">
+        <v>453</v>
+      </c>
     </row>
     <row r="188" spans="1:21" ht="85" x14ac:dyDescent="0.2">
       <c r="A188" s="25">
         <v>187</v>
       </c>
       <c r="B188" s="33" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="C188" s="25" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="D188" s="25" t="s">
         <v>33</v>
@@ -8416,16 +8762,19 @@
         <f t="array" ref="N188">SECTION_NAME(B188)</f>
         <v>encounter-start</v>
       </c>
+      <c r="P188" s="27" t="s">
+        <v>453</v>
+      </c>
     </row>
     <row r="189" spans="1:21" ht="187" x14ac:dyDescent="0.2">
       <c r="A189" s="25">
         <v>188</v>
       </c>
       <c r="B189" s="33" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="C189" s="25" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="D189" s="25" t="s">
         <v>28</v>
@@ -8438,7 +8787,7 @@
         <v>encounter-start</v>
       </c>
       <c r="T189" s="27" t="s">
-        <v>448</v>
+        <v>416</v>
       </c>
     </row>
     <row r="190" spans="1:21" ht="136" x14ac:dyDescent="0.2">
@@ -8446,10 +8795,10 @@
         <v>189</v>
       </c>
       <c r="B190" s="33" t="s">
+        <v>259</v>
+      </c>
+      <c r="C190" s="25" t="s">
         <v>264</v>
-      </c>
-      <c r="C190" s="25" t="s">
-        <v>269</v>
       </c>
       <c r="D190" s="25" t="s">
         <v>28</v>
@@ -8467,10 +8816,10 @@
         <v>190</v>
       </c>
       <c r="B191" s="33" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="C191" s="25" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="D191" s="25" t="s">
         <v>28</v>
@@ -8488,10 +8837,10 @@
         <v>191</v>
       </c>
       <c r="B192" s="33" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="C192" s="25" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="D192" s="25" t="s">
         <v>28</v>
@@ -8509,13 +8858,13 @@
         <v>192</v>
       </c>
       <c r="B193" s="33" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="C193" s="25" t="s">
-        <v>272</v>
+        <v>482</v>
       </c>
       <c r="D193" s="25" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="E193" s="25" t="s">
         <v>34</v>
@@ -8524,19 +8873,22 @@
         <f t="array" ref="N193">SECTION_NAME(B193)</f>
         <v>encounter-start</v>
       </c>
+      <c r="P193" s="27" t="s">
+        <v>453</v>
+      </c>
     </row>
     <row r="194" spans="1:20" ht="68" x14ac:dyDescent="0.2">
       <c r="A194" s="25">
         <v>193</v>
       </c>
       <c r="B194" s="33" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="C194" s="25" t="s">
-        <v>273</v>
+        <v>481</v>
       </c>
       <c r="D194" s="25" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="E194" s="25" t="s">
         <v>34</v>
@@ -8545,19 +8897,22 @@
         <f t="array" ref="N194">SECTION_NAME(B194)</f>
         <v>encounter-start</v>
       </c>
+      <c r="P194" s="27" t="s">
+        <v>453</v>
+      </c>
     </row>
     <row r="195" spans="1:20" ht="68" x14ac:dyDescent="0.2">
       <c r="A195" s="25">
         <v>194</v>
       </c>
       <c r="B195" s="33" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="C195" s="25" t="s">
-        <v>274</v>
+        <v>480</v>
       </c>
       <c r="D195" s="25" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="E195" s="25" t="s">
         <v>34</v>
@@ -8570,16 +8925,19 @@
         <f t="array" ref="N195">SECTION_NAME(B195)</f>
         <v>encounter-start</v>
       </c>
+      <c r="P195" s="27" t="s">
+        <v>453</v>
+      </c>
     </row>
     <row r="196" spans="1:20" ht="68" x14ac:dyDescent="0.2">
       <c r="A196" s="25">
         <v>195</v>
       </c>
       <c r="B196" s="33" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="C196" s="25" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="D196" s="25" t="s">
         <v>28</v>
@@ -8601,16 +8959,19 @@
         <v>196</v>
       </c>
       <c r="B197" s="33" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="C197" s="25" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="D197" s="25" t="s">
         <v>33</v>
       </c>
       <c r="E197" s="25" t="s">
         <v>38</v>
+      </c>
+      <c r="F197" s="25" t="s">
+        <v>469</v>
       </c>
     </row>
     <row r="198" spans="1:20" ht="102" x14ac:dyDescent="0.2">
@@ -8618,16 +8979,22 @@
         <v>197</v>
       </c>
       <c r="B198" s="33" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="C198" s="25" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="D198" s="25" t="s">
         <v>33</v>
       </c>
       <c r="E198" s="25" t="s">
         <v>34</v>
+      </c>
+      <c r="F198" s="25" t="s">
+        <v>470</v>
+      </c>
+      <c r="P198" s="27" t="s">
+        <v>456</v>
       </c>
     </row>
     <row r="199" spans="1:20" ht="85" x14ac:dyDescent="0.2">
@@ -8635,10 +9002,10 @@
         <v>198</v>
       </c>
       <c r="B199" s="33" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="C199" s="25" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="D199" s="25" t="s">
         <v>50</v>
@@ -8652,10 +9019,10 @@
         <v>199</v>
       </c>
       <c r="B200" s="33" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="C200" s="25" t="s">
-        <v>280</v>
+        <v>438</v>
       </c>
       <c r="D200" s="25" t="s">
         <v>50</v>
@@ -8669,10 +9036,10 @@
         <v>200</v>
       </c>
       <c r="B201" s="33" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="C201" s="25" t="s">
-        <v>281</v>
+        <v>439</v>
       </c>
       <c r="D201" s="25" t="s">
         <v>50</v>
@@ -8686,16 +9053,19 @@
         <v>201</v>
       </c>
       <c r="B202" s="33" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="C202" s="25" t="s">
-        <v>282</v>
+        <v>479</v>
       </c>
       <c r="D202" s="25" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E202" s="25" t="s">
         <v>34</v>
+      </c>
+      <c r="P202" s="27" t="s">
+        <v>456</v>
       </c>
     </row>
     <row r="203" spans="1:20" ht="102" x14ac:dyDescent="0.2">
@@ -8703,16 +9073,19 @@
         <v>202</v>
       </c>
       <c r="B203" s="33" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="C203" s="25" t="s">
-        <v>283</v>
+        <v>478</v>
       </c>
       <c r="D203" s="25" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E203" s="25" t="s">
         <v>34</v>
+      </c>
+      <c r="P203" s="27" t="s">
+        <v>456</v>
       </c>
     </row>
     <row r="204" spans="1:20" ht="102" x14ac:dyDescent="0.2">
@@ -8720,13 +9093,13 @@
         <v>203</v>
       </c>
       <c r="B204" s="33" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="C204" s="25" t="s">
-        <v>284</v>
+        <v>477</v>
       </c>
       <c r="D204" s="25" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E204" s="25" t="s">
         <v>34</v>
@@ -8739,16 +9112,19 @@
         <f t="array" ref="N204">SECTION_NAME(B204)</f>
         <v>encounter-discharge</v>
       </c>
+      <c r="P204" s="27" t="s">
+        <v>456</v>
+      </c>
     </row>
     <row r="205" spans="1:20" ht="85" x14ac:dyDescent="0.2">
       <c r="A205" s="25">
         <v>204</v>
       </c>
       <c r="B205" s="33" t="s">
-        <v>285</v>
+        <v>272</v>
       </c>
       <c r="C205" s="25" t="s">
-        <v>286</v>
+        <v>273</v>
       </c>
       <c r="D205" s="25" t="s">
         <v>33</v>
@@ -8756,8 +9132,11 @@
       <c r="E205" s="25" t="s">
         <v>38</v>
       </c>
+      <c r="F205" s="25" t="s">
+        <v>471</v>
+      </c>
       <c r="T205" s="27" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
     </row>
     <row r="206" spans="1:20" ht="85" x14ac:dyDescent="0.2">
@@ -8765,10 +9144,10 @@
         <v>205</v>
       </c>
       <c r="B206" s="33" t="s">
-        <v>285</v>
+        <v>272</v>
       </c>
       <c r="C206" s="25" t="s">
-        <v>288</v>
+        <v>275</v>
       </c>
       <c r="D206" s="25" t="s">
         <v>33</v>
@@ -8776,8 +9155,14 @@
       <c r="E206" s="25" t="s">
         <v>34</v>
       </c>
+      <c r="F206" s="25" t="s">
+        <v>472</v>
+      </c>
+      <c r="P206" s="27" t="s">
+        <v>459</v>
+      </c>
       <c r="T206" s="27" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
     </row>
     <row r="207" spans="1:20" ht="68" x14ac:dyDescent="0.2">
@@ -8785,10 +9170,10 @@
         <v>206</v>
       </c>
       <c r="B207" s="33" t="s">
-        <v>285</v>
+        <v>272</v>
       </c>
       <c r="C207" s="25" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
       <c r="D207" s="25" t="s">
         <v>28</v>
@@ -8805,7 +9190,7 @@
         <v>order-dispatch</v>
       </c>
       <c r="T207" s="27" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
     </row>
     <row r="208" spans="1:20" ht="119" x14ac:dyDescent="0.2">
@@ -8813,10 +9198,10 @@
         <v>207</v>
       </c>
       <c r="B208" s="33" t="s">
-        <v>285</v>
+        <v>272</v>
       </c>
       <c r="C208" s="25" t="s">
-        <v>290</v>
+        <v>277</v>
       </c>
       <c r="D208" s="25" t="s">
         <v>33</v>
@@ -8832,19 +9217,22 @@
         <f t="array" ref="N208">SECTION_NAME(B208)</f>
         <v>order-dispatch</v>
       </c>
+      <c r="P208" s="27" t="s">
+        <v>459</v>
+      </c>
       <c r="T208" s="27" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="209" spans="1:20" ht="85" x14ac:dyDescent="0.2">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="209" spans="1:20" ht="68" x14ac:dyDescent="0.2">
       <c r="A209" s="25">
         <v>208</v>
       </c>
       <c r="B209" s="33" t="s">
-        <v>291</v>
+        <v>278</v>
       </c>
       <c r="C209" s="25" t="s">
-        <v>292</v>
+        <v>421</v>
       </c>
       <c r="D209" s="25" t="s">
         <v>33</v>
@@ -8852,19 +9240,22 @@
       <c r="E209" s="25" t="s">
         <v>38</v>
       </c>
+      <c r="F209" s="25" t="s">
+        <v>473</v>
+      </c>
       <c r="T209" s="27" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="210" spans="1:20" ht="85" x14ac:dyDescent="0.2">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="210" spans="1:20" ht="68" x14ac:dyDescent="0.2">
       <c r="A210" s="25">
         <v>209</v>
       </c>
       <c r="B210" s="33" t="s">
-        <v>291</v>
+        <v>278</v>
       </c>
       <c r="C210" s="25" t="s">
-        <v>294</v>
+        <v>422</v>
       </c>
       <c r="D210" s="25" t="s">
         <v>33</v>
@@ -8872,8 +9263,14 @@
       <c r="E210" s="25" t="s">
         <v>34</v>
       </c>
+      <c r="F210" s="25" t="s">
+        <v>474</v>
+      </c>
+      <c r="P210" s="27" t="s">
+        <v>460</v>
+      </c>
       <c r="T210" s="27" t="s">
-        <v>293</v>
+        <v>279</v>
       </c>
     </row>
     <row r="211" spans="1:20" ht="68" x14ac:dyDescent="0.2">
@@ -8881,10 +9278,10 @@
         <v>210</v>
       </c>
       <c r="B211" s="33" t="s">
-        <v>291</v>
+        <v>278</v>
       </c>
       <c r="C211" s="25" t="s">
-        <v>295</v>
+        <v>423</v>
       </c>
       <c r="D211" s="25" t="s">
         <v>50</v>
@@ -8906,10 +9303,10 @@
         <v>211</v>
       </c>
       <c r="B212" s="33" t="s">
-        <v>291</v>
+        <v>278</v>
       </c>
       <c r="C212" s="25" t="s">
-        <v>296</v>
+        <v>424</v>
       </c>
       <c r="D212" s="25" t="s">
         <v>50</v>
@@ -8931,16 +9328,19 @@
         <v>212</v>
       </c>
       <c r="B213" s="33" t="s">
-        <v>291</v>
+        <v>278</v>
       </c>
       <c r="C213" s="25" t="s">
-        <v>297</v>
+        <v>425</v>
       </c>
       <c r="D213" s="25" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="E213" s="25" t="s">
-        <v>38</v>
+        <v>34</v>
+      </c>
+      <c r="P213" s="27" t="s">
+        <v>460</v>
       </c>
     </row>
     <row r="214" spans="1:20" ht="85" x14ac:dyDescent="0.2">
@@ -8948,33 +9348,36 @@
         <v>213</v>
       </c>
       <c r="B214" s="33" t="s">
-        <v>291</v>
+        <v>278</v>
       </c>
       <c r="C214" s="25" t="s">
-        <v>298</v>
+        <v>426</v>
       </c>
       <c r="D214" s="25" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="E214" s="25" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="215" spans="1:20" ht="255" x14ac:dyDescent="0.2">
+        <v>34</v>
+      </c>
+      <c r="P214" s="27" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="215" spans="1:20" ht="238" x14ac:dyDescent="0.2">
       <c r="A215" s="25">
         <v>214</v>
       </c>
       <c r="B215" s="33" t="s">
-        <v>291</v>
+        <v>278</v>
       </c>
       <c r="C215" s="25" t="s">
-        <v>299</v>
+        <v>427</v>
       </c>
       <c r="D215" s="25" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="E215" s="25" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="M215" s="30" t="str" cm="1">
         <f t="array" ref="M215">PAGE_NAME(B215)</f>
@@ -8984,22 +9387,28 @@
         <f t="array" ref="N215">SECTION_NAME(B215)</f>
         <v>order-select</v>
       </c>
+      <c r="P215" s="27" t="s">
+        <v>460</v>
+      </c>
     </row>
     <row r="216" spans="1:20" ht="170" x14ac:dyDescent="0.2">
       <c r="A216" s="25">
         <v>215</v>
       </c>
       <c r="B216" s="33" t="s">
-        <v>291</v>
+        <v>278</v>
       </c>
       <c r="C216" s="25" t="s">
-        <v>300</v>
+        <v>428</v>
       </c>
       <c r="D216" s="25" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="E216" s="25" t="s">
-        <v>38</v>
+        <v>34</v>
+      </c>
+      <c r="P216" s="27" t="s">
+        <v>460</v>
       </c>
     </row>
     <row r="217" spans="1:20" ht="51" x14ac:dyDescent="0.2">
@@ -9007,16 +9416,16 @@
         <v>216</v>
       </c>
       <c r="B217" s="33" t="s">
-        <v>291</v>
+        <v>278</v>
       </c>
       <c r="C217" s="25" t="s">
-        <v>301</v>
+        <v>429</v>
       </c>
       <c r="D217" s="25" t="s">
         <v>28</v>
       </c>
       <c r="E217" s="25" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="M217" s="30" t="str" cm="1">
         <f t="array" ref="M217">PAGE_NAME(B217)</f>
@@ -9032,16 +9441,19 @@
         <v>217</v>
       </c>
       <c r="B218" s="33" t="s">
-        <v>302</v>
+        <v>280</v>
       </c>
       <c r="C218" s="25" t="s">
-        <v>303</v>
+        <v>420</v>
       </c>
       <c r="D218" s="25" t="s">
         <v>33</v>
       </c>
       <c r="E218" s="25" t="s">
         <v>38</v>
+      </c>
+      <c r="F218" s="25" t="s">
+        <v>475</v>
       </c>
     </row>
     <row r="219" spans="1:20" ht="68" x14ac:dyDescent="0.2">
@@ -9049,16 +9461,22 @@
         <v>218</v>
       </c>
       <c r="B219" s="33" t="s">
-        <v>302</v>
+        <v>280</v>
       </c>
       <c r="C219" s="25" t="s">
-        <v>304</v>
+        <v>419</v>
       </c>
       <c r="D219" s="25" t="s">
         <v>33</v>
       </c>
       <c r="E219" s="25" t="s">
         <v>34</v>
+      </c>
+      <c r="F219" s="25" t="s">
+        <v>476</v>
+      </c>
+      <c r="P219" s="27" t="s">
+        <v>461</v>
       </c>
     </row>
     <row r="220" spans="1:20" ht="68" x14ac:dyDescent="0.2">
@@ -9066,10 +9484,10 @@
         <v>219</v>
       </c>
       <c r="B220" s="33" t="s">
-        <v>302</v>
+        <v>280</v>
       </c>
       <c r="C220" s="25" t="s">
-        <v>305</v>
+        <v>430</v>
       </c>
       <c r="D220" s="25" t="s">
         <v>28</v>
@@ -9091,16 +9509,19 @@
         <v>220</v>
       </c>
       <c r="B221" s="33" t="s">
-        <v>302</v>
+        <v>280</v>
       </c>
       <c r="C221" s="25" t="s">
-        <v>306</v>
+        <v>434</v>
       </c>
       <c r="D221" s="25" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="E221" s="25" t="s">
-        <v>38</v>
+        <v>34</v>
+      </c>
+      <c r="P221" s="27" t="s">
+        <v>461</v>
       </c>
     </row>
     <row r="222" spans="1:20" ht="136" x14ac:dyDescent="0.2">
@@ -9108,16 +9529,16 @@
         <v>221</v>
       </c>
       <c r="B222" s="33" t="s">
-        <v>302</v>
+        <v>280</v>
       </c>
       <c r="C222" s="25" t="s">
-        <v>307</v>
+        <v>435</v>
       </c>
       <c r="D222" s="25" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="E222" s="25" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="M222" s="30" t="str" cm="1">
         <f t="array" ref="M222">PAGE_NAME(B222)</f>
@@ -9127,22 +9548,28 @@
         <f t="array" ref="N222">SECTION_NAME(B222)</f>
         <v>order-sign</v>
       </c>
+      <c r="P222" s="27" t="s">
+        <v>461</v>
+      </c>
     </row>
     <row r="223" spans="1:20" ht="289" x14ac:dyDescent="0.2">
       <c r="A223" s="25">
         <v>222</v>
       </c>
       <c r="B223" s="33" t="s">
-        <v>302</v>
+        <v>280</v>
       </c>
       <c r="C223" s="25" t="s">
-        <v>308</v>
+        <v>436</v>
       </c>
       <c r="D223" s="25" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="E223" s="25" t="s">
-        <v>38</v>
+        <v>34</v>
+      </c>
+      <c r="P223" s="27" t="s">
+        <v>461</v>
       </c>
     </row>
     <row r="224" spans="1:20" ht="221" x14ac:dyDescent="0.2">
@@ -9150,27 +9577,30 @@
         <v>223</v>
       </c>
       <c r="B224" s="33" t="s">
-        <v>302</v>
+        <v>280</v>
       </c>
       <c r="C224" s="25" t="s">
-        <v>309</v>
+        <v>437</v>
       </c>
       <c r="D224" s="25" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="E224" s="25" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="225" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+        <v>34</v>
+      </c>
+      <c r="P224" s="27" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="225" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A225" s="25">
         <v>224</v>
       </c>
       <c r="B225" s="33" t="s">
-        <v>302</v>
+        <v>280</v>
       </c>
       <c r="C225" s="25" t="s">
-        <v>310</v>
+        <v>431</v>
       </c>
       <c r="D225" s="25" t="s">
         <v>28</v>
@@ -9187,15 +9617,15 @@
         <v>order-sign</v>
       </c>
     </row>
-    <row r="226" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A226" s="25">
         <v>225</v>
       </c>
       <c r="B226" s="33" t="s">
-        <v>302</v>
+        <v>280</v>
       </c>
       <c r="C226" s="25" t="s">
-        <v>311</v>
+        <v>432</v>
       </c>
       <c r="D226" s="25" t="s">
         <v>33</v>
@@ -9211,16 +9641,19 @@
         <f t="array" ref="N226">SECTION_NAME(B226)</f>
         <v>order-sign</v>
       </c>
-    </row>
-    <row r="227" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+      <c r="P226" s="27" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="227" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A227" s="25">
         <v>226</v>
       </c>
       <c r="B227" s="33" t="s">
-        <v>302</v>
+        <v>280</v>
       </c>
       <c r="C227" s="25" t="s">
-        <v>312</v>
+        <v>433</v>
       </c>
       <c r="D227" s="25" t="s">
         <v>33</v>
@@ -9237,15 +9670,15 @@
         <v>order-sign</v>
       </c>
     </row>
-    <row r="228" spans="1:14" ht="34" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:16" ht="34" x14ac:dyDescent="0.2">
       <c r="A228" s="25">
         <v>227</v>
       </c>
       <c r="B228" s="33" t="s">
-        <v>313</v>
+        <v>281</v>
       </c>
       <c r="C228" s="25" t="s">
-        <v>314</v>
+        <v>282</v>
       </c>
       <c r="D228" s="25" t="s">
         <v>50</v>
@@ -9262,15 +9695,15 @@
         <v>cards-profiles</v>
       </c>
     </row>
-    <row r="229" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:16" ht="17" x14ac:dyDescent="0.2">
       <c r="A229" s="25">
         <v>228</v>
       </c>
       <c r="B229" s="33" t="s">
-        <v>313</v>
+        <v>281</v>
       </c>
       <c r="C229" s="25" t="s">
-        <v>315</v>
+        <v>283</v>
       </c>
       <c r="D229" s="25" t="s">
         <v>50</v>
@@ -9287,15 +9720,15 @@
         <v>cards-profiles</v>
       </c>
     </row>
-    <row r="230" spans="1:14" ht="119" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:16" ht="119" x14ac:dyDescent="0.2">
       <c r="A230" s="25">
         <v>229</v>
       </c>
       <c r="B230" s="33" t="s">
-        <v>313</v>
+        <v>281</v>
       </c>
       <c r="C230" s="25" t="s">
-        <v>316</v>
+        <v>284</v>
       </c>
       <c r="D230" s="25" t="s">
         <v>50</v>
@@ -9312,15 +9745,15 @@
         <v>cards-profiles</v>
       </c>
     </row>
-    <row r="231" spans="1:14" ht="102" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:16" ht="102" x14ac:dyDescent="0.2">
       <c r="A231" s="25">
         <v>230</v>
       </c>
       <c r="B231" s="33" t="s">
-        <v>313</v>
+        <v>281</v>
       </c>
       <c r="C231" s="25" t="s">
-        <v>317</v>
+        <v>285</v>
       </c>
       <c r="D231" s="25" t="s">
         <v>50</v>
@@ -9337,15 +9770,15 @@
         <v>cards-profiles</v>
       </c>
     </row>
-    <row r="232" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A232" s="25">
         <v>231</v>
       </c>
       <c r="B232" s="33" t="s">
-        <v>313</v>
+        <v>281</v>
       </c>
       <c r="C232" s="25" t="s">
-        <v>318</v>
+        <v>286</v>
       </c>
       <c r="D232" s="25" t="s">
         <v>50</v>
@@ -9362,15 +9795,15 @@
         <v>cards-profiles</v>
       </c>
     </row>
-    <row r="233" spans="1:14" ht="85" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A233" s="25">
         <v>232</v>
       </c>
       <c r="B233" s="33" t="s">
-        <v>313</v>
+        <v>281</v>
       </c>
       <c r="C233" s="25" t="s">
-        <v>319</v>
+        <v>287</v>
       </c>
       <c r="D233" s="25" t="s">
         <v>50</v>
@@ -9387,15 +9820,15 @@
         <v>cards-profiles</v>
       </c>
     </row>
-    <row r="234" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A234" s="25">
         <v>233</v>
       </c>
       <c r="B234" s="33" t="s">
-        <v>313</v>
+        <v>281</v>
       </c>
       <c r="C234" s="25" t="s">
-        <v>320</v>
+        <v>288</v>
       </c>
       <c r="D234" s="25" t="s">
         <v>50</v>
@@ -9412,15 +9845,15 @@
         <v>cards-profiles</v>
       </c>
     </row>
-    <row r="235" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A235" s="25">
         <v>234</v>
       </c>
       <c r="B235" s="33" t="s">
-        <v>313</v>
+        <v>281</v>
       </c>
       <c r="C235" s="25" t="s">
-        <v>321</v>
+        <v>289</v>
       </c>
       <c r="D235" s="25" t="s">
         <v>50</v>
@@ -9437,15 +9870,15 @@
         <v>cards-profiles</v>
       </c>
     </row>
-    <row r="236" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A236" s="25">
         <v>235</v>
       </c>
       <c r="B236" s="33" t="s">
-        <v>313</v>
+        <v>281</v>
       </c>
       <c r="C236" s="25" t="s">
-        <v>322</v>
+        <v>290</v>
       </c>
       <c r="D236" s="25" t="s">
         <v>50</v>
@@ -9462,15 +9895,15 @@
         <v>cards-profiles</v>
       </c>
     </row>
-    <row r="237" spans="1:14" ht="102" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:16" ht="102" x14ac:dyDescent="0.2">
       <c r="A237" s="25">
         <v>236</v>
       </c>
       <c r="B237" s="33" t="s">
-        <v>313</v>
+        <v>281</v>
       </c>
       <c r="C237" s="25" t="s">
-        <v>323</v>
+        <v>291</v>
       </c>
       <c r="D237" s="25" t="s">
         <v>50</v>
@@ -9487,15 +9920,15 @@
         <v>cards-profiles</v>
       </c>
     </row>
-    <row r="238" spans="1:14" ht="85" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A238" s="25">
         <v>237</v>
       </c>
       <c r="B238" s="33" t="s">
-        <v>313</v>
+        <v>281</v>
       </c>
       <c r="C238" s="25" t="s">
-        <v>324</v>
+        <v>292</v>
       </c>
       <c r="D238" s="25" t="s">
         <v>50</v>
@@ -9512,15 +9945,15 @@
         <v>cards-profiles</v>
       </c>
     </row>
-    <row r="239" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A239" s="25">
         <v>238</v>
       </c>
       <c r="B239" s="33" t="s">
-        <v>313</v>
+        <v>281</v>
       </c>
       <c r="C239" s="25" t="s">
-        <v>325</v>
+        <v>293</v>
       </c>
       <c r="D239" s="25" t="s">
         <v>50</v>
@@ -9537,15 +9970,15 @@
         <v>cards-profiles</v>
       </c>
     </row>
-    <row r="240" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A240" s="25">
         <v>239</v>
       </c>
       <c r="B240" s="33" t="s">
-        <v>313</v>
+        <v>281</v>
       </c>
       <c r="C240" s="25" t="s">
-        <v>326</v>
+        <v>294</v>
       </c>
       <c r="D240" s="25" t="s">
         <v>50</v>
@@ -9562,15 +9995,15 @@
         <v>cards-profiles</v>
       </c>
     </row>
-    <row r="241" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:20" ht="51" x14ac:dyDescent="0.2">
       <c r="A241" s="25">
         <v>240</v>
       </c>
       <c r="B241" s="33" t="s">
-        <v>313</v>
+        <v>281</v>
       </c>
       <c r="C241" s="25" t="s">
-        <v>327</v>
+        <v>295</v>
       </c>
       <c r="D241" s="25" t="s">
         <v>50</v>
@@ -9587,15 +10020,15 @@
         <v>cards-profiles</v>
       </c>
     </row>
-    <row r="242" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:20" ht="51" x14ac:dyDescent="0.2">
       <c r="A242" s="25">
         <v>241</v>
       </c>
       <c r="B242" s="33" t="s">
-        <v>313</v>
+        <v>281</v>
       </c>
       <c r="C242" s="25" t="s">
-        <v>328</v>
+        <v>296</v>
       </c>
       <c r="D242" s="25" t="s">
         <v>105</v>
@@ -9612,15 +10045,15 @@
         <v>cards-profiles</v>
       </c>
     </row>
-    <row r="243" spans="1:14" ht="34" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:20" ht="34" x14ac:dyDescent="0.2">
       <c r="A243" s="25">
         <v>242</v>
       </c>
       <c r="B243" s="33" t="s">
-        <v>313</v>
+        <v>281</v>
       </c>
       <c r="C243" s="25" t="s">
-        <v>329</v>
+        <v>297</v>
       </c>
       <c r="D243" s="25" t="s">
         <v>50</v>
@@ -9637,15 +10070,15 @@
         <v>cards-profiles</v>
       </c>
     </row>
-    <row r="244" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:20" ht="51" x14ac:dyDescent="0.2">
       <c r="A244" s="25">
         <v>243</v>
       </c>
       <c r="B244" s="33" t="s">
-        <v>330</v>
+        <v>298</v>
       </c>
       <c r="C244" s="25" t="s">
-        <v>331</v>
+        <v>299</v>
       </c>
       <c r="D244" s="25" t="s">
         <v>33</v>
@@ -9661,16 +10094,19 @@
         <f t="array" ref="N244">SECTION_NAME(B244)</f>
         <v>potential-crd-response-types</v>
       </c>
-    </row>
-    <row r="245" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+      <c r="P244" s="27" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="245" spans="1:20" ht="51" x14ac:dyDescent="0.2">
       <c r="A245" s="25">
         <v>244</v>
       </c>
       <c r="B245" s="33" t="s">
-        <v>330</v>
+        <v>298</v>
       </c>
       <c r="C245" s="25" t="s">
-        <v>332</v>
+        <v>300</v>
       </c>
       <c r="D245" s="25" t="s">
         <v>33</v>
@@ -9686,16 +10122,19 @@
         <f t="array" ref="N245">SECTION_NAME(B245)</f>
         <v>potential-crd-response-types</v>
       </c>
-    </row>
-    <row r="246" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+      <c r="P245" s="27" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="246" spans="1:20" ht="51" x14ac:dyDescent="0.2">
       <c r="A246" s="25">
         <v>245</v>
       </c>
       <c r="B246" s="33" t="s">
-        <v>330</v>
+        <v>298</v>
       </c>
       <c r="C246" s="25" t="s">
-        <v>333</v>
+        <v>301</v>
       </c>
       <c r="D246" s="25" t="s">
         <v>33</v>
@@ -9711,16 +10150,19 @@
         <f t="array" ref="N246">SECTION_NAME(B246)</f>
         <v>potential-crd-response-types</v>
       </c>
-    </row>
-    <row r="247" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+      <c r="P246" s="27" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="247" spans="1:20" ht="51" x14ac:dyDescent="0.2">
       <c r="A247" s="25">
         <v>246</v>
       </c>
       <c r="B247" s="33" t="s">
-        <v>330</v>
+        <v>298</v>
       </c>
       <c r="C247" s="25" t="s">
-        <v>334</v>
+        <v>302</v>
       </c>
       <c r="D247" s="25" t="s">
         <v>50</v>
@@ -9737,15 +10179,15 @@
         <v>potential-crd-response-types</v>
       </c>
     </row>
-    <row r="248" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:20" ht="68" x14ac:dyDescent="0.2">
       <c r="A248" s="25">
         <v>247</v>
       </c>
       <c r="B248" s="33" t="s">
-        <v>330</v>
+        <v>298</v>
       </c>
       <c r="C248" s="25" t="s">
-        <v>335</v>
+        <v>303</v>
       </c>
       <c r="D248" s="25" t="s">
         <v>33</v>
@@ -9762,15 +10204,15 @@
         <v>potential-crd-response-types</v>
       </c>
     </row>
-    <row r="249" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:20" ht="68" x14ac:dyDescent="0.2">
       <c r="A249" s="25">
         <v>248</v>
       </c>
       <c r="B249" s="33" t="s">
-        <v>330</v>
+        <v>298</v>
       </c>
       <c r="C249" s="25" t="s">
-        <v>336</v>
+        <v>304</v>
       </c>
       <c r="D249" s="25" t="s">
         <v>33</v>
@@ -9787,15 +10229,15 @@
         <v>potential-crd-response-types</v>
       </c>
     </row>
-    <row r="250" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:20" ht="68" x14ac:dyDescent="0.2">
       <c r="A250" s="25">
         <v>249</v>
       </c>
       <c r="B250" s="33" t="s">
-        <v>330</v>
+        <v>298</v>
       </c>
       <c r="C250" s="25" t="s">
-        <v>337</v>
+        <v>305</v>
       </c>
       <c r="D250" s="25" t="s">
         <v>33</v>
@@ -9812,15 +10254,15 @@
         <v>potential-crd-response-types</v>
       </c>
     </row>
-    <row r="251" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:20" ht="51" x14ac:dyDescent="0.2">
       <c r="A251" s="25">
         <v>250</v>
       </c>
       <c r="B251" s="33" t="s">
-        <v>330</v>
+        <v>298</v>
       </c>
       <c r="C251" s="25" t="s">
-        <v>338</v>
+        <v>306</v>
       </c>
       <c r="D251" s="25" t="s">
         <v>28</v>
@@ -9837,15 +10279,15 @@
         <v>potential-crd-response-types</v>
       </c>
     </row>
-    <row r="252" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:20" ht="51" x14ac:dyDescent="0.2">
       <c r="A252" s="25">
         <v>251</v>
       </c>
       <c r="B252" s="33" t="s">
-        <v>330</v>
+        <v>298</v>
       </c>
       <c r="C252" s="25" t="s">
-        <v>339</v>
+        <v>307</v>
       </c>
       <c r="D252" s="25" t="s">
         <v>28</v>
@@ -9862,15 +10304,15 @@
         <v>potential-crd-response-types</v>
       </c>
     </row>
-    <row r="253" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:20" ht="68" x14ac:dyDescent="0.2">
       <c r="A253" s="25">
         <v>252</v>
       </c>
       <c r="B253" s="33" t="s">
-        <v>330</v>
+        <v>298</v>
       </c>
       <c r="C253" s="25" t="s">
-        <v>340</v>
+        <v>308</v>
       </c>
       <c r="D253" s="25" t="s">
         <v>33</v>
@@ -9887,15 +10329,15 @@
         <v>potential-crd-response-types</v>
       </c>
     </row>
-    <row r="254" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:20" ht="68" x14ac:dyDescent="0.2">
       <c r="A254" s="25">
         <v>253</v>
       </c>
       <c r="B254" s="33" t="s">
-        <v>330</v>
+        <v>298</v>
       </c>
       <c r="C254" s="25" t="s">
-        <v>341</v>
+        <v>309</v>
       </c>
       <c r="D254" s="25" t="s">
         <v>105</v>
@@ -9912,18 +10354,18 @@
         <v>potential-crd-response-types</v>
       </c>
     </row>
-    <row r="255" spans="1:14" ht="85" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:20" ht="102" x14ac:dyDescent="0.2">
       <c r="A255" s="25">
         <v>254</v>
       </c>
       <c r="B255" s="33" t="s">
-        <v>330</v>
+        <v>298</v>
       </c>
       <c r="C255" s="25" t="s">
-        <v>342</v>
+        <v>310</v>
       </c>
       <c r="D255" s="25" t="s">
-        <v>33</v>
+        <v>206</v>
       </c>
       <c r="E255" s="25" t="s">
         <v>34</v>
@@ -9936,22 +10378,34 @@
         <f t="array" ref="N255">SECTION_NAME(B255)</f>
         <v>potential-crd-response-types</v>
       </c>
-    </row>
-    <row r="256" spans="1:14" ht="85" x14ac:dyDescent="0.2">
+      <c r="P255" s="27" t="s">
+        <v>445</v>
+      </c>
+      <c r="T255" s="27" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="256" spans="1:20" ht="85" x14ac:dyDescent="0.2">
       <c r="A256" s="25">
         <v>255</v>
       </c>
       <c r="B256" s="33" t="s">
-        <v>330</v>
+        <v>298</v>
       </c>
       <c r="C256" s="25" t="s">
-        <v>343</v>
+        <v>311</v>
       </c>
       <c r="D256" s="25" t="s">
         <v>33</v>
       </c>
       <c r="E256" s="25" t="s">
         <v>34</v>
+      </c>
+      <c r="G256" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="H256" s="27" t="s">
+        <v>493</v>
       </c>
       <c r="M256" s="30" t="str" cm="1">
         <f t="array" ref="M256">PAGE_NAME(B256)</f>
@@ -9961,16 +10415,19 @@
         <f t="array" ref="N256">SECTION_NAME(B256)</f>
         <v>potential-crd-response-types</v>
       </c>
-    </row>
-    <row r="257" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+      <c r="P256" s="27" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="257" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A257" s="25">
         <v>256</v>
       </c>
       <c r="B257" s="33" t="s">
-        <v>330</v>
+        <v>298</v>
       </c>
       <c r="C257" s="25" t="s">
-        <v>344</v>
+        <v>312</v>
       </c>
       <c r="D257" s="25" t="s">
         <v>50</v>
@@ -9987,15 +10444,15 @@
         <v>potential-crd-response-types</v>
       </c>
     </row>
-    <row r="258" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A258" s="25">
         <v>257</v>
       </c>
       <c r="B258" s="33" t="s">
-        <v>330</v>
+        <v>298</v>
       </c>
       <c r="C258" s="25" t="s">
-        <v>345</v>
+        <v>313</v>
       </c>
       <c r="D258" s="25" t="s">
         <v>50</v>
@@ -10012,15 +10469,15 @@
         <v>potential-crd-response-types</v>
       </c>
     </row>
-    <row r="259" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A259" s="25">
         <v>258</v>
       </c>
       <c r="B259" s="33" t="s">
-        <v>346</v>
+        <v>314</v>
       </c>
       <c r="C259" s="25" t="s">
-        <v>347</v>
+        <v>315</v>
       </c>
       <c r="D259" s="25" t="s">
         <v>33</v>
@@ -10037,15 +10494,15 @@
         <v>external-reference</v>
       </c>
     </row>
-    <row r="260" spans="1:14" ht="34" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:16" ht="34" x14ac:dyDescent="0.2">
       <c r="A260" s="25">
         <v>259</v>
       </c>
       <c r="B260" s="33" t="s">
-        <v>346</v>
+        <v>314</v>
       </c>
       <c r="C260" s="25" t="s">
-        <v>348</v>
+        <v>316</v>
       </c>
       <c r="D260" s="25" t="s">
         <v>33</v>
@@ -10062,15 +10519,15 @@
         <v>external-reference</v>
       </c>
     </row>
-    <row r="261" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A261" s="25">
         <v>260</v>
       </c>
       <c r="B261" s="33" t="s">
-        <v>346</v>
+        <v>314</v>
       </c>
       <c r="C261" s="25" t="s">
-        <v>349</v>
+        <v>317</v>
       </c>
       <c r="D261" s="25" t="s">
         <v>50</v>
@@ -10087,15 +10544,15 @@
         <v>external-reference</v>
       </c>
     </row>
-    <row r="262" spans="1:14" ht="85" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A262" s="25">
         <v>261</v>
       </c>
       <c r="B262" s="33" t="s">
-        <v>346</v>
+        <v>314</v>
       </c>
       <c r="C262" s="25" t="s">
-        <v>350</v>
+        <v>318</v>
       </c>
       <c r="D262" s="25" t="s">
         <v>50</v>
@@ -10112,15 +10569,15 @@
         <v>external-reference</v>
       </c>
     </row>
-    <row r="263" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A263" s="25">
         <v>262</v>
       </c>
       <c r="B263" s="33" t="s">
-        <v>351</v>
+        <v>319</v>
       </c>
       <c r="C263" s="25" t="s">
-        <v>352</v>
+        <v>320</v>
       </c>
       <c r="D263" s="25" t="s">
         <v>33</v>
@@ -10137,15 +10594,15 @@
         <v>coverage-information</v>
       </c>
     </row>
-    <row r="264" spans="1:14" ht="85" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A264" s="25">
         <v>263</v>
       </c>
       <c r="B264" s="33" t="s">
-        <v>351</v>
+        <v>319</v>
       </c>
       <c r="C264" s="25" t="s">
-        <v>353</v>
+        <v>321</v>
       </c>
       <c r="D264" s="25" t="s">
         <v>33</v>
@@ -10161,16 +10618,19 @@
         <f t="array" ref="N264">SECTION_NAME(B264)</f>
         <v>coverage-information</v>
       </c>
-    </row>
-    <row r="265" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+      <c r="P264" s="27" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="265" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A265" s="25">
         <v>264</v>
       </c>
       <c r="B265" s="33" t="s">
-        <v>351</v>
+        <v>319</v>
       </c>
       <c r="C265" s="25" t="s">
-        <v>354</v>
+        <v>322</v>
       </c>
       <c r="D265" s="25" t="s">
         <v>33</v>
@@ -10187,15 +10647,15 @@
         <v>coverage-information</v>
       </c>
     </row>
-    <row r="266" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A266" s="25">
         <v>265</v>
       </c>
       <c r="B266" s="33" t="s">
-        <v>351</v>
+        <v>319</v>
       </c>
       <c r="C266" s="25" t="s">
-        <v>355</v>
+        <v>323</v>
       </c>
       <c r="D266" s="25" t="s">
         <v>33</v>
@@ -10212,15 +10672,15 @@
         <v>coverage-information</v>
       </c>
     </row>
-    <row r="267" spans="1:14" ht="34" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:16" ht="34" x14ac:dyDescent="0.2">
       <c r="A267" s="25">
         <v>266</v>
       </c>
       <c r="B267" s="33" t="s">
-        <v>351</v>
+        <v>319</v>
       </c>
       <c r="C267" s="25" t="s">
-        <v>356</v>
+        <v>324</v>
       </c>
       <c r="D267" s="25" t="s">
         <v>28</v>
@@ -10237,15 +10697,15 @@
         <v>coverage-information</v>
       </c>
     </row>
-    <row r="268" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A268" s="25">
         <v>267</v>
       </c>
       <c r="B268" s="33" t="s">
-        <v>351</v>
+        <v>319</v>
       </c>
       <c r="C268" s="25" t="s">
-        <v>357</v>
+        <v>325</v>
       </c>
       <c r="D268" s="25" t="s">
         <v>157</v>
@@ -10262,15 +10722,15 @@
         <v>coverage-information</v>
       </c>
     </row>
-    <row r="269" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A269" s="25">
         <v>268</v>
       </c>
       <c r="B269" s="33" t="s">
-        <v>351</v>
+        <v>319</v>
       </c>
       <c r="C269" s="25" t="s">
-        <v>358</v>
+        <v>326</v>
       </c>
       <c r="D269" s="25" t="s">
         <v>50</v>
@@ -10287,15 +10747,15 @@
         <v>coverage-information</v>
       </c>
     </row>
-    <row r="270" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A270" s="25">
         <v>269</v>
       </c>
       <c r="B270" s="33" t="s">
-        <v>351</v>
+        <v>319</v>
       </c>
       <c r="C270" s="25" t="s">
-        <v>359</v>
+        <v>327</v>
       </c>
       <c r="D270" s="25" t="s">
         <v>50</v>
@@ -10312,15 +10772,15 @@
         <v>coverage-information</v>
       </c>
     </row>
-    <row r="271" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A271" s="25">
         <v>270</v>
       </c>
       <c r="B271" s="33" t="s">
-        <v>351</v>
+        <v>319</v>
       </c>
       <c r="C271" s="25" t="s">
-        <v>360</v>
+        <v>328</v>
       </c>
       <c r="D271" s="25" t="s">
         <v>50</v>
@@ -10337,15 +10797,15 @@
         <v>coverage-information</v>
       </c>
     </row>
-    <row r="272" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A272" s="25">
         <v>271</v>
       </c>
       <c r="B272" s="33" t="s">
-        <v>351</v>
+        <v>319</v>
       </c>
       <c r="C272" s="25" t="s">
-        <v>361</v>
+        <v>329</v>
       </c>
       <c r="D272" s="25" t="s">
         <v>105</v>
@@ -10362,15 +10822,15 @@
         <v>coverage-information</v>
       </c>
     </row>
-    <row r="273" spans="1:14" ht="85" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A273" s="25">
         <v>272</v>
       </c>
       <c r="B273" s="33" t="s">
-        <v>351</v>
+        <v>319</v>
       </c>
       <c r="C273" s="25" t="s">
-        <v>362</v>
+        <v>330</v>
       </c>
       <c r="D273" s="25" t="s">
         <v>33</v>
@@ -10387,15 +10847,15 @@
         <v>coverage-information</v>
       </c>
     </row>
-    <row r="274" spans="1:14" ht="85" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A274" s="25">
         <v>273</v>
       </c>
       <c r="B274" s="33" t="s">
-        <v>351</v>
+        <v>319</v>
       </c>
       <c r="C274" s="25" t="s">
-        <v>363</v>
+        <v>331</v>
       </c>
       <c r="D274" s="25" t="s">
         <v>33</v>
@@ -10412,15 +10872,15 @@
         <v>coverage-information</v>
       </c>
     </row>
-    <row r="275" spans="1:14" ht="102" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:16" ht="102" x14ac:dyDescent="0.2">
       <c r="A275" s="25">
         <v>274</v>
       </c>
       <c r="B275" s="33" t="s">
-        <v>351</v>
+        <v>319</v>
       </c>
       <c r="C275" s="25" t="s">
-        <v>364</v>
+        <v>332</v>
       </c>
       <c r="D275" s="25" t="s">
         <v>33</v>
@@ -10437,15 +10897,15 @@
         <v>coverage-information</v>
       </c>
     </row>
-    <row r="276" spans="1:14" ht="85" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A276" s="25">
         <v>275</v>
       </c>
       <c r="B276" s="33" t="s">
-        <v>351</v>
+        <v>319</v>
       </c>
       <c r="C276" s="25" t="s">
-        <v>365</v>
+        <v>333</v>
       </c>
       <c r="D276" s="25" t="s">
         <v>33</v>
@@ -10462,15 +10922,15 @@
         <v>coverage-information</v>
       </c>
     </row>
-    <row r="277" spans="1:14" ht="85" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A277" s="25">
         <v>276</v>
       </c>
       <c r="B277" s="33" t="s">
-        <v>351</v>
+        <v>319</v>
       </c>
       <c r="C277" s="25" t="s">
-        <v>366</v>
+        <v>334</v>
       </c>
       <c r="D277" s="25" t="s">
         <v>33</v>
@@ -10487,15 +10947,15 @@
         <v>coverage-information</v>
       </c>
     </row>
-    <row r="278" spans="1:14" ht="85" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A278" s="25">
         <v>277</v>
       </c>
       <c r="B278" s="33" t="s">
-        <v>351</v>
+        <v>319</v>
       </c>
       <c r="C278" s="25" t="s">
-        <v>367</v>
+        <v>335</v>
       </c>
       <c r="D278" s="25" t="s">
         <v>33</v>
@@ -10512,15 +10972,15 @@
         <v>coverage-information</v>
       </c>
     </row>
-    <row r="279" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A279" s="25">
         <v>278</v>
       </c>
       <c r="B279" s="33" t="s">
-        <v>351</v>
+        <v>319</v>
       </c>
       <c r="C279" s="25" t="s">
-        <v>368</v>
+        <v>336</v>
       </c>
       <c r="D279" s="25" t="s">
         <v>33</v>
@@ -10536,16 +10996,19 @@
         <f t="array" ref="N279">SECTION_NAME(B279)</f>
         <v>coverage-information</v>
       </c>
-    </row>
-    <row r="280" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+      <c r="P279" s="27" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="280" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A280" s="25">
         <v>279</v>
       </c>
       <c r="B280" s="33" t="s">
-        <v>351</v>
+        <v>319</v>
       </c>
       <c r="C280" s="25" t="s">
-        <v>369</v>
+        <v>337</v>
       </c>
       <c r="D280" s="25" t="s">
         <v>33</v>
@@ -10562,15 +11025,15 @@
         <v>coverage-information</v>
       </c>
     </row>
-    <row r="281" spans="1:14" ht="85" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A281" s="25">
         <v>280</v>
       </c>
       <c r="B281" s="33" t="s">
-        <v>351</v>
+        <v>319</v>
       </c>
       <c r="C281" s="25" t="s">
-        <v>370</v>
+        <v>338</v>
       </c>
       <c r="D281" s="25" t="s">
         <v>33</v>
@@ -10586,16 +11049,19 @@
         <f t="array" ref="N281">SECTION_NAME(B281)</f>
         <v>coverage-information</v>
       </c>
-    </row>
-    <row r="282" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+      <c r="P281" s="27" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="282" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A282" s="25">
         <v>281</v>
       </c>
       <c r="B282" s="33" t="s">
-        <v>351</v>
+        <v>319</v>
       </c>
       <c r="C282" s="25" t="s">
-        <v>371</v>
+        <v>339</v>
       </c>
       <c r="D282" s="25" t="s">
         <v>28</v>
@@ -10612,15 +11078,15 @@
         <v>coverage-information</v>
       </c>
     </row>
-    <row r="283" spans="1:14" ht="85" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A283" s="25">
         <v>282</v>
       </c>
       <c r="B283" s="33" t="s">
-        <v>372</v>
+        <v>340</v>
       </c>
       <c r="C283" s="25" t="s">
-        <v>373</v>
+        <v>341</v>
       </c>
       <c r="D283" s="25" t="s">
         <v>50</v>
@@ -10637,15 +11103,15 @@
         <v>propose-alternate-request</v>
       </c>
     </row>
-    <row r="284" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A284" s="25">
         <v>283</v>
       </c>
       <c r="B284" s="33" t="s">
-        <v>372</v>
+        <v>340</v>
       </c>
       <c r="C284" s="25" t="s">
-        <v>374</v>
+        <v>342</v>
       </c>
       <c r="D284" s="25" t="s">
         <v>50</v>
@@ -10662,15 +11128,15 @@
         <v>propose-alternate-request</v>
       </c>
     </row>
-    <row r="285" spans="1:14" ht="102" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:16" ht="102" x14ac:dyDescent="0.2">
       <c r="A285" s="25">
         <v>284</v>
       </c>
       <c r="B285" s="33" t="s">
-        <v>372</v>
+        <v>340</v>
       </c>
       <c r="C285" s="25" t="s">
-        <v>375</v>
+        <v>343</v>
       </c>
       <c r="D285" s="25" t="s">
         <v>33</v>
@@ -10686,16 +11152,19 @@
         <f t="array" ref="N285">SECTION_NAME(B285)</f>
         <v>propose-alternate-request</v>
       </c>
-    </row>
-    <row r="286" spans="1:14" ht="153" x14ac:dyDescent="0.2">
+      <c r="P285" s="27" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="286" spans="1:16" ht="153" x14ac:dyDescent="0.2">
       <c r="A286" s="25">
         <v>285</v>
       </c>
       <c r="B286" s="33" t="s">
-        <v>372</v>
+        <v>340</v>
       </c>
       <c r="C286" s="25" t="s">
-        <v>376</v>
+        <v>344</v>
       </c>
       <c r="D286" s="25" t="s">
         <v>33</v>
@@ -10711,16 +11180,19 @@
         <f t="array" ref="N286">SECTION_NAME(B286)</f>
         <v>propose-alternate-request</v>
       </c>
-    </row>
-    <row r="287" spans="1:14" ht="136" x14ac:dyDescent="0.2">
+      <c r="P286" s="27" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="287" spans="1:16" ht="136" x14ac:dyDescent="0.2">
       <c r="A287" s="25">
         <v>286</v>
       </c>
       <c r="B287" s="33" t="s">
-        <v>372</v>
+        <v>340</v>
       </c>
       <c r="C287" s="25" t="s">
-        <v>377</v>
+        <v>345</v>
       </c>
       <c r="D287" s="25" t="s">
         <v>33</v>
@@ -10736,16 +11208,19 @@
         <f t="array" ref="N287">SECTION_NAME(B287)</f>
         <v>propose-alternate-request</v>
       </c>
-    </row>
-    <row r="288" spans="1:14" ht="187" x14ac:dyDescent="0.2">
+      <c r="P287" s="27" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="288" spans="1:16" ht="187" x14ac:dyDescent="0.2">
       <c r="A288" s="25">
         <v>287</v>
       </c>
       <c r="B288" s="33" t="s">
-        <v>372</v>
+        <v>340</v>
       </c>
       <c r="C288" s="25" t="s">
-        <v>378</v>
+        <v>346</v>
       </c>
       <c r="D288" s="25" t="s">
         <v>33</v>
@@ -10761,16 +11236,19 @@
         <f t="array" ref="N288">SECTION_NAME(B288)</f>
         <v>propose-alternate-request</v>
       </c>
-    </row>
-    <row r="289" spans="1:14" ht="136" x14ac:dyDescent="0.2">
+      <c r="P288" s="27" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="289" spans="1:16" ht="136" x14ac:dyDescent="0.2">
       <c r="A289" s="25">
         <v>288</v>
       </c>
       <c r="B289" s="33" t="s">
-        <v>372</v>
+        <v>340</v>
       </c>
       <c r="C289" s="25" t="s">
-        <v>379</v>
+        <v>347</v>
       </c>
       <c r="D289" s="25" t="s">
         <v>33</v>
@@ -10786,16 +11264,19 @@
         <f t="array" ref="N289">SECTION_NAME(B289)</f>
         <v>propose-alternate-request</v>
       </c>
-    </row>
-    <row r="290" spans="1:14" ht="136" x14ac:dyDescent="0.2">
+      <c r="P289" s="27" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="290" spans="1:16" ht="136" x14ac:dyDescent="0.2">
       <c r="A290" s="25">
         <v>289</v>
       </c>
       <c r="B290" s="33" t="s">
-        <v>372</v>
+        <v>340</v>
       </c>
       <c r="C290" s="25" t="s">
-        <v>380</v>
+        <v>348</v>
       </c>
       <c r="D290" s="25" t="s">
         <v>33</v>
@@ -10811,16 +11292,19 @@
         <f t="array" ref="N290">SECTION_NAME(B290)</f>
         <v>propose-alternate-request</v>
       </c>
-    </row>
-    <row r="291" spans="1:14" ht="136" x14ac:dyDescent="0.2">
+      <c r="P290" s="27" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="291" spans="1:16" ht="136" x14ac:dyDescent="0.2">
       <c r="A291" s="25">
         <v>290</v>
       </c>
       <c r="B291" s="33" t="s">
-        <v>372</v>
+        <v>340</v>
       </c>
       <c r="C291" s="25" t="s">
-        <v>381</v>
+        <v>349</v>
       </c>
       <c r="D291" s="25" t="s">
         <v>33</v>
@@ -10836,16 +11320,19 @@
         <f t="array" ref="N291">SECTION_NAME(B291)</f>
         <v>propose-alternate-request</v>
       </c>
-    </row>
-    <row r="292" spans="1:14" ht="153" x14ac:dyDescent="0.2">
+      <c r="P291" s="27" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="292" spans="1:16" ht="153" x14ac:dyDescent="0.2">
       <c r="A292" s="25">
         <v>291</v>
       </c>
       <c r="B292" s="33" t="s">
-        <v>382</v>
+        <v>350</v>
       </c>
       <c r="C292" s="25" t="s">
-        <v>383</v>
+        <v>351</v>
       </c>
       <c r="D292" s="25" t="s">
         <v>33</v>
@@ -10857,16 +11344,19 @@
         <f t="array" ref="N292">SECTION_NAME(B292)</f>
         <v>identify-additional-orders-as-companionsprerequisites-for-current-order</v>
       </c>
-    </row>
-    <row r="293" spans="1:14" ht="153" x14ac:dyDescent="0.2">
+      <c r="P292" s="27" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="293" spans="1:16" ht="153" x14ac:dyDescent="0.2">
       <c r="A293" s="25">
         <v>292</v>
       </c>
       <c r="B293" s="33" t="s">
-        <v>382</v>
+        <v>350</v>
       </c>
       <c r="C293" s="25" t="s">
-        <v>384</v>
+        <v>352</v>
       </c>
       <c r="D293" s="25" t="s">
         <v>33</v>
@@ -10878,16 +11368,19 @@
         <f t="array" ref="N293">SECTION_NAME(B293)</f>
         <v>identify-additional-orders-as-companionsprerequisites-for-current-order</v>
       </c>
-    </row>
-    <row r="294" spans="1:14" ht="170" x14ac:dyDescent="0.2">
+      <c r="P293" s="27" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="294" spans="1:16" ht="170" x14ac:dyDescent="0.2">
       <c r="A294" s="25">
         <v>293</v>
       </c>
       <c r="B294" s="33" t="s">
-        <v>382</v>
+        <v>350</v>
       </c>
       <c r="C294" s="25" t="s">
-        <v>385</v>
+        <v>353</v>
       </c>
       <c r="D294" s="25" t="s">
         <v>33</v>
@@ -10899,16 +11392,19 @@
         <f t="array" ref="N294">SECTION_NAME(B294)</f>
         <v>identify-additional-orders-as-companionsprerequisites-for-current-order</v>
       </c>
-    </row>
-    <row r="295" spans="1:14" ht="119" x14ac:dyDescent="0.2">
+      <c r="P294" s="27" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="295" spans="1:16" ht="119" x14ac:dyDescent="0.2">
       <c r="A295" s="25">
         <v>294</v>
       </c>
       <c r="B295" s="33" t="s">
-        <v>382</v>
+        <v>350</v>
       </c>
       <c r="C295" s="25" t="s">
-        <v>386</v>
+        <v>354</v>
       </c>
       <c r="D295" s="25" t="s">
         <v>33</v>
@@ -10920,16 +11416,19 @@
         <f t="array" ref="N295">SECTION_NAME(B295)</f>
         <v>identify-additional-orders-as-companionsprerequisites-for-current-order</v>
       </c>
-    </row>
-    <row r="296" spans="1:14" ht="136" x14ac:dyDescent="0.2">
+      <c r="P295" s="27" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="296" spans="1:16" ht="136" x14ac:dyDescent="0.2">
       <c r="A296" s="25">
         <v>295</v>
       </c>
       <c r="B296" s="33" t="s">
-        <v>382</v>
+        <v>350</v>
       </c>
       <c r="C296" s="25" t="s">
-        <v>387</v>
+        <v>355</v>
       </c>
       <c r="D296" s="25" t="s">
         <v>33</v>
@@ -10941,16 +11440,19 @@
         <f t="array" ref="N296">SECTION_NAME(B296)</f>
         <v>identify-additional-orders-as-companionsprerequisites-for-current-order</v>
       </c>
-    </row>
-    <row r="297" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+      <c r="P296" s="27" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="297" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A297" s="25">
         <v>296</v>
       </c>
       <c r="B297" s="33" t="s">
-        <v>388</v>
+        <v>356</v>
       </c>
       <c r="C297" s="25" t="s">
-        <v>389</v>
+        <v>357</v>
       </c>
       <c r="D297" s="25" t="s">
         <v>28</v>
@@ -10959,15 +11461,15 @@
         <v>38</v>
       </c>
     </row>
-    <row r="298" spans="1:14" ht="34" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A298" s="25">
         <v>297</v>
       </c>
       <c r="B298" s="33" t="s">
-        <v>388</v>
+        <v>356</v>
       </c>
       <c r="C298" s="25" t="s">
-        <v>390</v>
+        <v>358</v>
       </c>
       <c r="D298" s="25" t="s">
         <v>33</v>
@@ -10983,16 +11485,19 @@
         <f t="array" ref="N298">SECTION_NAME(B298)</f>
         <v>request-form-completion</v>
       </c>
-    </row>
-    <row r="299" spans="1:14" ht="34" x14ac:dyDescent="0.2">
+      <c r="P298" s="27" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="299" spans="1:16" ht="34" x14ac:dyDescent="0.2">
       <c r="A299" s="25">
         <v>298</v>
       </c>
       <c r="B299" s="33" t="s">
-        <v>388</v>
+        <v>356</v>
       </c>
       <c r="C299" s="25" t="s">
-        <v>391</v>
+        <v>359</v>
       </c>
       <c r="D299" s="25" t="s">
         <v>50</v>
@@ -11009,15 +11514,15 @@
         <v>request-form-completion</v>
       </c>
     </row>
-    <row r="300" spans="1:14" ht="102" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:16" ht="102" x14ac:dyDescent="0.2">
       <c r="A300" s="25">
         <v>299</v>
       </c>
       <c r="B300" s="33" t="s">
-        <v>388</v>
+        <v>356</v>
       </c>
       <c r="C300" s="25" t="s">
-        <v>392</v>
+        <v>360</v>
       </c>
       <c r="D300" s="25" t="s">
         <v>33</v>
@@ -11034,15 +11539,15 @@
         <v>request-form-completion</v>
       </c>
     </row>
-    <row r="301" spans="1:14" ht="153" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:16" ht="153" x14ac:dyDescent="0.2">
       <c r="A301" s="25">
         <v>300</v>
       </c>
       <c r="B301" s="33" t="s">
-        <v>388</v>
+        <v>356</v>
       </c>
       <c r="C301" s="25" t="s">
-        <v>393</v>
+        <v>361</v>
       </c>
       <c r="D301" s="25" t="s">
         <v>50</v>
@@ -11059,15 +11564,15 @@
         <v>request-form-completion</v>
       </c>
     </row>
-    <row r="302" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A302" s="25">
         <v>301</v>
       </c>
       <c r="B302" s="33" t="s">
-        <v>388</v>
+        <v>356</v>
       </c>
       <c r="C302" s="25" t="s">
-        <v>394</v>
+        <v>362</v>
       </c>
       <c r="D302" s="25" t="s">
         <v>50</v>
@@ -11084,15 +11589,15 @@
         <v>request-form-completion</v>
       </c>
     </row>
-    <row r="303" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A303" s="25">
         <v>302</v>
       </c>
       <c r="B303" s="33" t="s">
-        <v>395</v>
+        <v>363</v>
       </c>
       <c r="C303" s="25" t="s">
-        <v>396</v>
+        <v>364</v>
       </c>
       <c r="D303" s="25" t="s">
         <v>28</v>
@@ -11109,15 +11614,15 @@
         <v>create-or-update-coverage-information</v>
       </c>
     </row>
-    <row r="304" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A304" s="25">
         <v>303</v>
       </c>
       <c r="B304" s="33" t="s">
-        <v>395</v>
+        <v>363</v>
       </c>
       <c r="C304" s="25" t="s">
-        <v>397</v>
+        <v>365</v>
       </c>
       <c r="D304" s="25" t="s">
         <v>33</v>
@@ -11133,16 +11638,19 @@
         <f t="array" ref="N304">SECTION_NAME(B304)</f>
         <v>create-or-update-coverage-information</v>
       </c>
-    </row>
-    <row r="305" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+      <c r="P304" s="27" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="305" spans="1:20" ht="68" x14ac:dyDescent="0.2">
       <c r="A305" s="25">
         <v>304</v>
       </c>
       <c r="B305" s="33" t="s">
-        <v>395</v>
+        <v>363</v>
       </c>
       <c r="C305" s="25" t="s">
-        <v>398</v>
+        <v>366</v>
       </c>
       <c r="D305" s="25" t="s">
         <v>28</v>
@@ -11159,15 +11667,15 @@
         <v>create-or-update-coverage-information</v>
       </c>
     </row>
-    <row r="306" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:20" ht="51" x14ac:dyDescent="0.2">
       <c r="A306" s="25">
         <v>305</v>
       </c>
       <c r="B306" s="33" t="s">
-        <v>395</v>
+        <v>363</v>
       </c>
       <c r="C306" s="25" t="s">
-        <v>399</v>
+        <v>367</v>
       </c>
       <c r="D306" s="25" t="s">
         <v>157</v>
@@ -11184,15 +11692,15 @@
         <v>create-or-update-coverage-information</v>
       </c>
     </row>
-    <row r="307" spans="1:14" ht="102" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:20" ht="102" x14ac:dyDescent="0.2">
       <c r="A307" s="25">
         <v>306</v>
       </c>
       <c r="B307" s="33" t="s">
-        <v>395</v>
+        <v>363</v>
       </c>
       <c r="C307" s="25" t="s">
-        <v>400</v>
+        <v>368</v>
       </c>
       <c r="D307" s="25" t="s">
         <v>33</v>
@@ -11209,15 +11717,15 @@
         <v>create-or-update-coverage-information</v>
       </c>
     </row>
-    <row r="308" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:20" ht="68" x14ac:dyDescent="0.2">
       <c r="A308" s="25">
         <v>307</v>
       </c>
       <c r="B308" s="33" t="s">
-        <v>401</v>
+        <v>369</v>
       </c>
       <c r="C308" s="25" t="s">
-        <v>402</v>
+        <v>370</v>
       </c>
       <c r="D308" s="25" t="s">
         <v>28</v>
@@ -11234,15 +11742,15 @@
         <v>launch-smart-application</v>
       </c>
     </row>
-    <row r="309" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:20" ht="68" x14ac:dyDescent="0.2">
       <c r="A309" s="25">
         <v>308</v>
       </c>
       <c r="B309" s="33" t="s">
-        <v>403</v>
+        <v>371</v>
       </c>
       <c r="C309" s="25" t="s">
-        <v>404</v>
+        <v>372</v>
       </c>
       <c r="D309" s="25" t="s">
         <v>33</v>
@@ -11258,16 +11766,19 @@
         <f t="array" ref="N309">SECTION_NAME(B309)</f>
         <v>suppressing-guidance</v>
       </c>
-    </row>
-    <row r="310" spans="1:14" ht="85" x14ac:dyDescent="0.2">
+      <c r="P309" s="27" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="310" spans="1:20" ht="85" x14ac:dyDescent="0.2">
       <c r="A310" s="25">
         <v>309</v>
       </c>
       <c r="B310" s="33" t="s">
-        <v>405</v>
+        <v>373</v>
       </c>
       <c r="C310" s="25" t="s">
-        <v>406</v>
+        <v>374</v>
       </c>
       <c r="D310" s="25" t="s">
         <v>50</v>
@@ -11284,15 +11795,15 @@
         <v>impact-on-payer-processes</v>
       </c>
     </row>
-    <row r="311" spans="1:14" ht="136" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:20" ht="136" x14ac:dyDescent="0.2">
       <c r="A311" s="25">
         <v>310</v>
       </c>
       <c r="B311" s="33" t="s">
-        <v>405</v>
+        <v>373</v>
       </c>
       <c r="C311" s="25" t="s">
-        <v>407</v>
+        <v>375</v>
       </c>
       <c r="D311" s="25" t="s">
         <v>50</v>
@@ -11309,15 +11820,15 @@
         <v>impact-on-payer-processes</v>
       </c>
     </row>
-    <row r="312" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:20" ht="68" x14ac:dyDescent="0.2">
       <c r="A312" s="25">
         <v>311</v>
       </c>
       <c r="B312" s="33" t="s">
-        <v>405</v>
+        <v>373</v>
       </c>
       <c r="C312" s="25" t="s">
-        <v>408</v>
+        <v>376</v>
       </c>
       <c r="D312" s="25" t="s">
         <v>28</v>
@@ -11334,132 +11845,338 @@
         <v>impact-on-payer-processes</v>
       </c>
     </row>
-    <row r="313" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B313" s="33"/>
-    </row>
-    <row r="314" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B314" s="33"/>
+    <row r="313" spans="1:20" ht="170" x14ac:dyDescent="0.2">
+      <c r="A313" s="25">
+        <v>312</v>
+      </c>
+      <c r="B313" s="33" t="s">
+        <v>489</v>
+      </c>
+      <c r="C313" s="25" t="s">
+        <v>490</v>
+      </c>
+      <c r="D313" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="E313" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="P313" s="27" t="s">
+        <v>440</v>
+      </c>
+      <c r="T313" s="27" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="314" spans="1:20" ht="51" x14ac:dyDescent="0.2">
+      <c r="A314" s="25">
+        <v>313</v>
+      </c>
+      <c r="B314" s="33" t="s">
+        <v>492</v>
+      </c>
+      <c r="C314" s="25" t="s">
+        <v>491</v>
+      </c>
+      <c r="D314" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="E314" s="25" t="s">
+        <v>34</v>
+      </c>
       <c r="M314" s="30" t="str" cm="1">
         <f t="array" ref="M314">PAGE_NAME(B314)</f>
-        <v/>
+        <v>CapabilityStatement-crd-client</v>
       </c>
       <c r="N314" s="30" t="str" cm="1">
         <f t="array" ref="N314">SECTION_NAME(B314)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="315" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B315" s="33"/>
+        <v>mode1</v>
+      </c>
+      <c r="P314" s="27" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="315" spans="1:20" ht="34" x14ac:dyDescent="0.2">
+      <c r="A315" s="25">
+        <v>314</v>
+      </c>
+      <c r="B315" s="33" t="s">
+        <v>489</v>
+      </c>
+      <c r="C315" s="25" t="s">
+        <v>494</v>
+      </c>
+      <c r="D315" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="E315" s="25" t="s">
+        <v>34</v>
+      </c>
       <c r="M315" s="30" t="str" cm="1">
         <f t="array" ref="M315">PAGE_NAME(B315)</f>
-        <v/>
+        <v>CapabilityStatement-crd-client</v>
       </c>
       <c r="N315" s="30" t="str" cm="1">
         <f t="array" ref="N315">SECTION_NAME(B315)</f>
         <v/>
       </c>
-    </row>
-    <row r="316" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B316" s="33"/>
+      <c r="P315" s="27" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="316" spans="1:20" ht="51" x14ac:dyDescent="0.2">
+      <c r="A316" s="25">
+        <v>315</v>
+      </c>
+      <c r="B316" s="33" t="s">
+        <v>489</v>
+      </c>
+      <c r="C316" s="25" t="s">
+        <v>495</v>
+      </c>
+      <c r="D316" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="E316" s="25" t="s">
+        <v>34</v>
+      </c>
       <c r="M316" s="30" t="str" cm="1">
         <f t="array" ref="M316">PAGE_NAME(B316)</f>
-        <v/>
+        <v>CapabilityStatement-crd-client</v>
       </c>
       <c r="N316" s="30" t="str" cm="1">
         <f t="array" ref="N316">SECTION_NAME(B316)</f>
         <v/>
       </c>
-    </row>
-    <row r="317" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B317" s="33"/>
+      <c r="P316" s="27" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="317" spans="1:20" ht="51" x14ac:dyDescent="0.2">
+      <c r="A317" s="25">
+        <v>316</v>
+      </c>
+      <c r="B317" s="33" t="s">
+        <v>489</v>
+      </c>
+      <c r="C317" s="25" t="s">
+        <v>496</v>
+      </c>
+      <c r="D317" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="E317" s="25" t="s">
+        <v>34</v>
+      </c>
       <c r="M317" s="30" t="str" cm="1">
         <f t="array" ref="M317">PAGE_NAME(B317)</f>
-        <v/>
+        <v>CapabilityStatement-crd-client</v>
       </c>
       <c r="N317" s="30" t="str" cm="1">
         <f t="array" ref="N317">SECTION_NAME(B317)</f>
         <v/>
       </c>
-    </row>
-    <row r="318" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B318" s="33"/>
+      <c r="P317" s="27" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="318" spans="1:20" ht="68" x14ac:dyDescent="0.2">
+      <c r="A318" s="25">
+        <v>317</v>
+      </c>
+      <c r="B318" s="33" t="s">
+        <v>489</v>
+      </c>
+      <c r="C318" s="25" t="s">
+        <v>498</v>
+      </c>
+      <c r="D318" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="E318" s="25" t="s">
+        <v>34</v>
+      </c>
       <c r="M318" s="30" t="str" cm="1">
         <f t="array" ref="M318">PAGE_NAME(B318)</f>
-        <v/>
+        <v>CapabilityStatement-crd-client</v>
       </c>
       <c r="N318" s="30" t="str" cm="1">
         <f t="array" ref="N318">SECTION_NAME(B318)</f>
         <v/>
       </c>
-    </row>
-    <row r="319" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B319" s="33"/>
+      <c r="P318" s="27" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="319" spans="1:20" ht="51" x14ac:dyDescent="0.2">
+      <c r="A319" s="25">
+        <v>318</v>
+      </c>
+      <c r="B319" s="33" t="s">
+        <v>489</v>
+      </c>
+      <c r="C319" s="25" t="s">
+        <v>497</v>
+      </c>
+      <c r="D319" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="E319" s="25" t="s">
+        <v>34</v>
+      </c>
       <c r="M319" s="30" t="str" cm="1">
         <f t="array" ref="M319">PAGE_NAME(B319)</f>
-        <v/>
+        <v>CapabilityStatement-crd-client</v>
       </c>
       <c r="N319" s="30" t="str" cm="1">
         <f t="array" ref="N319">SECTION_NAME(B319)</f>
         <v/>
       </c>
-    </row>
-    <row r="320" spans="1:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B320" s="33"/>
+      <c r="P319" s="27" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="320" spans="1:20" ht="51" x14ac:dyDescent="0.2">
+      <c r="A320" s="25">
+        <v>319</v>
+      </c>
+      <c r="B320" s="33" t="s">
+        <v>489</v>
+      </c>
+      <c r="C320" s="25" t="s">
+        <v>499</v>
+      </c>
+      <c r="D320" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="E320" s="25" t="s">
+        <v>34</v>
+      </c>
       <c r="M320" s="30" t="str" cm="1">
         <f t="array" ref="M320">PAGE_NAME(B320)</f>
-        <v/>
+        <v>CapabilityStatement-crd-client</v>
       </c>
       <c r="N320" s="30" t="str" cm="1">
         <f t="array" ref="N320">SECTION_NAME(B320)</f>
         <v/>
       </c>
-    </row>
-    <row r="321" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B321" s="33"/>
+      <c r="P320" s="27" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="321" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+      <c r="A321" s="25">
+        <v>320</v>
+      </c>
+      <c r="B321" s="33" t="s">
+        <v>489</v>
+      </c>
+      <c r="C321" s="25" t="s">
+        <v>500</v>
+      </c>
+      <c r="D321" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="E321" s="25" t="s">
+        <v>34</v>
+      </c>
       <c r="M321" s="30" t="str" cm="1">
         <f t="array" ref="M321">PAGE_NAME(B321)</f>
-        <v/>
+        <v>CapabilityStatement-crd-client</v>
       </c>
       <c r="N321" s="30" t="str" cm="1">
         <f t="array" ref="N321">SECTION_NAME(B321)</f>
         <v/>
       </c>
-    </row>
-    <row r="322" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B322" s="33"/>
+      <c r="P321" s="27" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="322" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+      <c r="A322" s="25">
+        <v>321</v>
+      </c>
+      <c r="B322" s="33" t="s">
+        <v>489</v>
+      </c>
+      <c r="C322" s="25" t="s">
+        <v>501</v>
+      </c>
+      <c r="D322" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="E322" s="25" t="s">
+        <v>34</v>
+      </c>
       <c r="M322" s="30" t="str" cm="1">
         <f t="array" ref="M322">PAGE_NAME(B322)</f>
-        <v/>
+        <v>CapabilityStatement-crd-client</v>
       </c>
       <c r="N322" s="30" t="str" cm="1">
         <f t="array" ref="N322">SECTION_NAME(B322)</f>
         <v/>
       </c>
-    </row>
-    <row r="323" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B323" s="33"/>
+      <c r="P322" s="27" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="323" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+      <c r="A323" s="25">
+        <v>322</v>
+      </c>
+      <c r="B323" s="33" t="s">
+        <v>489</v>
+      </c>
+      <c r="C323" s="25" t="s">
+        <v>502</v>
+      </c>
+      <c r="D323" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="E323" s="25" t="s">
+        <v>34</v>
+      </c>
       <c r="M323" s="30" t="str" cm="1">
         <f t="array" ref="M323">PAGE_NAME(B323)</f>
-        <v/>
+        <v>CapabilityStatement-crd-client</v>
       </c>
       <c r="N323" s="30" t="str" cm="1">
         <f t="array" ref="N323">SECTION_NAME(B323)</f>
         <v/>
       </c>
-    </row>
-    <row r="324" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B324" s="33"/>
+      <c r="P323" s="27" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="324" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+      <c r="A324" s="25">
+        <v>323</v>
+      </c>
+      <c r="B324" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="C324" s="25" t="s">
+        <v>504</v>
+      </c>
+      <c r="D324" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="E324" s="25" t="s">
+        <v>34</v>
+      </c>
       <c r="M324" s="30" t="str" cm="1">
         <f t="array" ref="M324">PAGE_NAME(B324)</f>
-        <v/>
+        <v>foundation</v>
       </c>
       <c r="N324" s="30" t="str" cm="1">
         <f t="array" ref="N324">SECTION_NAME(B324)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="325" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B325" s="33"/>
+        <v>crd-access-tokens</v>
+      </c>
+      <c r="P324" s="27" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="325" spans="1:16" ht="17" x14ac:dyDescent="0.2">
       <c r="M325" s="30" t="str" cm="1">
         <f t="array" ref="M325">PAGE_NAME(B325)</f>
         <v/>
@@ -11469,7 +12186,7 @@
         <v/>
       </c>
     </row>
-    <row r="326" spans="2:14" ht="17" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:16" ht="17" x14ac:dyDescent="0.2">
       <c r="M326" s="30" t="str" cm="1">
         <f t="array" ref="M326">PAGE_NAME(B326)</f>
         <v/>
@@ -11479,7 +12196,7 @@
         <v/>
       </c>
     </row>
-    <row r="327" spans="2:14" ht="17" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:16" ht="17" x14ac:dyDescent="0.2">
       <c r="M327" s="30" t="str" cm="1">
         <f t="array" ref="M327">PAGE_NAME(B327)</f>
         <v/>
@@ -11489,7 +12206,7 @@
         <v/>
       </c>
     </row>
-    <row r="328" spans="2:14" ht="17" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:16" ht="17" x14ac:dyDescent="0.2">
       <c r="M328" s="30" t="str" cm="1">
         <f t="array" ref="M328">PAGE_NAME(B328)</f>
         <v/>
@@ -11499,7 +12216,7 @@
         <v/>
       </c>
     </row>
-    <row r="329" spans="2:14" ht="17" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:16" ht="17" x14ac:dyDescent="0.2">
       <c r="M329" s="30" t="str" cm="1">
         <f t="array" ref="M329">PAGE_NAME(B329)</f>
         <v/>
@@ -11509,7 +12226,7 @@
         <v/>
       </c>
     </row>
-    <row r="330" spans="2:14" ht="17" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:16" ht="17" x14ac:dyDescent="0.2">
       <c r="M330" s="30" t="str" cm="1">
         <f t="array" ref="M330">PAGE_NAME(B330)</f>
         <v/>
@@ -11519,7 +12236,7 @@
         <v/>
       </c>
     </row>
-    <row r="331" spans="2:14" ht="17" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:16" ht="17" x14ac:dyDescent="0.2">
       <c r="M331" s="30" t="str" cm="1">
         <f t="array" ref="M331">PAGE_NAME(B331)</f>
         <v/>
@@ -11529,7 +12246,7 @@
         <v/>
       </c>
     </row>
-    <row r="332" spans="2:14" ht="17" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:16" ht="17" x14ac:dyDescent="0.2">
       <c r="M332" s="30" t="str" cm="1">
         <f t="array" ref="M332">PAGE_NAME(B332)</f>
         <v/>
@@ -11539,7 +12256,7 @@
         <v/>
       </c>
     </row>
-    <row r="333" spans="2:14" ht="17" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:16" ht="17" x14ac:dyDescent="0.2">
       <c r="M333" s="30" t="str" cm="1">
         <f t="array" ref="M333">PAGE_NAME(B333)</f>
         <v/>
@@ -11549,7 +12266,7 @@
         <v/>
       </c>
     </row>
-    <row r="334" spans="2:14" ht="17" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:16" ht="17" x14ac:dyDescent="0.2">
       <c r="M334" s="30" t="str" cm="1">
         <f t="array" ref="M334">PAGE_NAME(B334)</f>
         <v/>
@@ -11559,7 +12276,7 @@
         <v/>
       </c>
     </row>
-    <row r="335" spans="2:14" ht="17" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:16" ht="17" x14ac:dyDescent="0.2">
       <c r="M335" s="30" t="str" cm="1">
         <f t="array" ref="M335">PAGE_NAME(B335)</f>
         <v/>
@@ -11569,7 +12286,7 @@
         <v/>
       </c>
     </row>
-    <row r="336" spans="2:14" ht="17" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:16" ht="17" x14ac:dyDescent="0.2">
       <c r="M336" s="30" t="str" cm="1">
         <f t="array" ref="M336">PAGE_NAME(B336)</f>
         <v/>
@@ -11660,6 +12377,7 @@
       </c>
     </row>
     <row r="345" spans="2:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="B345" s="33"/>
       <c r="M345" s="30" t="str" cm="1">
         <f t="array" ref="M345">PAGE_NAME(B345)</f>
         <v/>
@@ -11670,7 +12388,6 @@
       </c>
     </row>
     <row r="346" spans="2:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="B346" s="33"/>
       <c r="M346" s="30" t="str" cm="1">
         <f t="array" ref="M346">PAGE_NAME(B346)</f>
         <v/>
@@ -12550,18 +13267,8 @@
         <v/>
       </c>
     </row>
-    <row r="434" spans="13:14" ht="17" x14ac:dyDescent="0.2">
-      <c r="M434" s="30" t="str" cm="1">
-        <f t="array" ref="M434">PAGE_NAME(B434)</f>
-        <v/>
-      </c>
-      <c r="N434" s="30" t="str" cm="1">
-        <f t="array" ref="N434">SECTION_NAME(B434)</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:T312" xr:uid="{0272D98A-080C-3945-A7E0-CB54FB3A65A9}"/>
+  <autoFilter ref="A1:T433" xr:uid="{0272D98A-080C-3945-A7E0-CB54FB3A65A9}"/>
   <phoneticPr fontId="19" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="B3" r:id="rId1" location="mustsupport" xr:uid="{184F9D0E-560D-48E2-89DF-D828B07B1E5F}"/>
@@ -12825,6 +13532,18 @@
     <hyperlink ref="B43" r:id="rId259" location="additional-data-retrieval" xr:uid="{4CA5E12F-5D9B-4E70-BFE0-23078A77DAD2}"/>
     <hyperlink ref="B61" r:id="rId260" location="query-notes" xr:uid="{F352642C-5E42-44B7-A229-709C7B04AFA5}"/>
     <hyperlink ref="B35" r:id="rId261" location="enabling-a-crd-server" xr:uid="{29492AB6-A2B3-4D6D-AE1A-D0642733CC57}"/>
+    <hyperlink ref="B313" r:id="rId262" xr:uid="{5A7044E4-ECC6-8346-910D-AA03F675DEC7}"/>
+    <hyperlink ref="B316" r:id="rId263" xr:uid="{2FA4B1FA-85FD-AD4D-BEA5-6604BC45F12B}"/>
+    <hyperlink ref="B314" r:id="rId264" location="mode1" xr:uid="{F4E24FAE-9A70-494A-B2FE-AAD9593C3236}"/>
+    <hyperlink ref="B315" r:id="rId265" xr:uid="{0075B5F5-9BDE-E54B-BDA4-E62690EA943E}"/>
+    <hyperlink ref="B317" r:id="rId266" xr:uid="{2A4FA271-3D53-DC4C-973D-015A52C5D891}"/>
+    <hyperlink ref="B318" r:id="rId267" xr:uid="{97761A23-9D1E-7046-A0AA-9D2D1BBC7816}"/>
+    <hyperlink ref="B319" r:id="rId268" xr:uid="{E985FC82-CF70-104C-96FF-8F6FCA25F8C0}"/>
+    <hyperlink ref="B320" r:id="rId269" xr:uid="{4970B588-B14E-EC4E-BA9F-F56016F887CD}"/>
+    <hyperlink ref="B321" r:id="rId270" xr:uid="{97C55971-E2C3-7244-81CA-BD37FB24BFA3}"/>
+    <hyperlink ref="B322" r:id="rId271" xr:uid="{43BF7D95-9CEA-1040-9742-52552CCADCCF}"/>
+    <hyperlink ref="B323" r:id="rId272" xr:uid="{18B2CDF4-D33C-B14E-A306-E6D686E42A3C}"/>
+    <hyperlink ref="B324" r:id="rId273" location="crd-access-tokens" xr:uid="{B501E1B5-4CEF-F54F-B165-9093BF92BC2D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -12834,19 +13553,19 @@
           <x14:formula1>
             <xm:f>'Column Data'!$B$2:$B$3</xm:f>
           </x14:formula1>
-          <xm:sqref>G298:G1048576 G2:G296</xm:sqref>
+          <xm:sqref>G2:G296 G298:G1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{4866B9BF-5615-6646-965F-909D4D65F2A5}">
           <x14:formula1>
             <xm:f>'Column Data'!$A$2:$A$7</xm:f>
           </x14:formula1>
-          <xm:sqref>D298:D1048576 D2:D296</xm:sqref>
+          <xm:sqref>D2:D296 D298:D1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{F4FB27A2-804E-CB49-B85C-BBEE0C688B4F}">
           <x14:formula1>
             <xm:f>'Column Data'!$D$2:$D$4</xm:f>
           </x14:formula1>
-          <xm:sqref>I298:I1048576 K298:K1048576 K2:K296 I2:I296</xm:sqref>
+          <xm:sqref>K2:K296 I2:I296 I298:I1048576 K298:K1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -12864,83 +13583,83 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="409" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="40" t="s">
-        <v>444</v>
-      </c>
-      <c r="B1" s="40"/>
+      <c r="A1" s="48" t="s">
+        <v>412</v>
+      </c>
+      <c r="B1" s="48"/>
     </row>
     <row r="2" spans="1:2" ht="82" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="40"/>
-      <c r="B2" s="40"/>
+      <c r="A2" s="48"/>
+      <c r="B2" s="48"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>409</v>
+        <v>377</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>410</v>
+        <v>378</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>411</v>
+        <v>379</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>412</v>
+        <v>380</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>413</v>
+        <v>381</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>414</v>
+        <v>382</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>415</v>
+        <v>383</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>416</v>
+        <v>384</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>417</v>
+        <v>385</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>418</v>
+        <v>386</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>419</v>
+        <v>387</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>420</v>
+        <v>388</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>421</v>
+        <v>389</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>422</v>
+        <v>390</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>423</v>
+        <v>391</v>
       </c>
       <c r="B13" s="21" t="s">
-        <v>424</v>
+        <v>392</v>
       </c>
     </row>
   </sheetData>
@@ -12965,19 +13684,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>412</v>
+        <v>380</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>425</v>
+        <v>393</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>426</v>
+        <v>394</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>427</v>
+        <v>395</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>428</v>
+        <v>396</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
@@ -12985,13 +13704,13 @@
         <v>0.1</v>
       </c>
       <c r="B2" t="s">
-        <v>429</v>
+        <v>397</v>
       </c>
       <c r="C2" s="22" t="s">
-        <v>430</v>
+        <v>398</v>
       </c>
       <c r="D2" t="s">
-        <v>431</v>
+        <v>399</v>
       </c>
       <c r="E2" s="23">
         <v>45583</v>
@@ -13012,13 +13731,13 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>432</v>
+        <v>400</v>
       </c>
       <c r="B1" t="s">
         <v>12</v>
       </c>
       <c r="C1" t="s">
-        <v>433</v>
+        <v>401</v>
       </c>
       <c r="D1" t="s">
         <v>14</v>
@@ -13032,10 +13751,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>434</v>
+        <v>402</v>
       </c>
       <c r="D2" t="s">
-        <v>435</v>
+        <v>403</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -13046,10 +13765,10 @@
         <v>0</v>
       </c>
       <c r="C3" t="s">
-        <v>436</v>
+        <v>404</v>
       </c>
       <c r="D3" t="s">
-        <v>437</v>
+        <v>405</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -13057,7 +13776,7 @@
         <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>438</v>
+        <v>406</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -13090,19 +13809,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="b5a44311-ed64-4a72-909f-c9dc6973bde2" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="eebd8b74-b9de-41b2-9247-c010c4973c2b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <Description xmlns="eebd8b74-b9de-41b2-9247-c010c4973c2b" xsi:nil="true"/>
-    <SortOrder xmlns="eebd8b74-b9de-41b2-9247-c010c4973c2b" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100EC335ED7BB179244BF94A0DFE64544DC" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d3a0f66abe5d2a0564332877ab55d3f7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="eebd8b74-b9de-41b2-9247-c010c4973c2b" xmlns:ns3="b7009bbd-f938-489b-a530-f05273710fff" xmlns:ns4="b5a44311-ed64-4a72-909f-c9dc6973bde2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ec7ca2ee893ff8a0f61d4046c6461645" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="eebd8b74-b9de-41b2-9247-c010c4973c2b"/>
@@ -13356,6 +14062,19 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="b5a44311-ed64-4a72-909f-c9dc6973bde2" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="eebd8b74-b9de-41b2-9247-c010c4973c2b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <Description xmlns="eebd8b74-b9de-41b2-9247-c010c4973c2b" xsi:nil="true"/>
+    <SortOrder xmlns="eebd8b74-b9de-41b2-9247-c010c4973c2b" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA84097F-5807-4DCF-92C6-48C9EE26CFB8}">
   <ds:schemaRefs>
@@ -13365,24 +14084,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19B0E317-5E0E-4728-AB3F-40F2C2B957FB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="b5a44311-ed64-4a72-909f-c9dc6973bde2"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="b7009bbd-f938-489b-a530-f05273710fff"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="eebd8b74-b9de-41b2-9247-c010c4973c2b"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{45EEC221-F5CD-4DEF-B390-EE14E23A8785}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -13400,4 +14101,22 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19B0E317-5E0E-4728-AB3F-40F2C2B957FB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="b5a44311-ed64-4a72-909f-c9dc6973bde2"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="b7009bbd-f938-489b-a530-f05273710fff"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="eebd8b74-b9de-41b2-9247-c010c4973c2b"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>